--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$108</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$107</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4183" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4145" uniqueCount="669">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.0</t>
+    <t>3.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:45:50+00:00</t>
+    <t>2023-04-26T08:27:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -326,6 +326,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
@@ -400,10 +404,6 @@
     <t>Meta.versionId</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-</t>
-  </si>
-  <si>
     <t>Observation.meta.lastUpdated</t>
   </si>
   <si>
@@ -456,14 +456,7 @@
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
-</t>
-  </si>
-  <si>
     <t>Meta.profile</t>
-  </si>
-  <si>
-    <t>Observation.meta.profile:MesObservationStepsByDay</t>
   </si>
   <si>
     <t>Observation.meta.security</t>
@@ -2421,10 +2414,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP108"/>
+  <dimension ref="A1:AP107"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.5" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -2848,7 +2841,7 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s" s="2">
         <v>88</v>
@@ -2932,7 +2925,7 @@
         <v>100</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>78</v>
@@ -2944,7 +2937,7 @@
         <v>78</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>78</v>
@@ -2955,10 +2948,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2981,13 +2974,13 @@
         <v>78</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -3038,7 +3031,7 @@
         <v>78</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>76</v>
@@ -3062,7 +3055,7 @@
         <v>78</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>78</v>
@@ -3073,14 +3066,14 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
@@ -3099,16 +3092,16 @@
         <v>78</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -3146,19 +3139,19 @@
         <v>78</v>
       </c>
       <c r="AB6" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AC6" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AD6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE6" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>76</v>
@@ -3170,7 +3163,7 @@
         <v>100</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>78</v>
@@ -3182,7 +3175,7 @@
         <v>78</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>78</v>
@@ -3193,10 +3186,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3222,13 +3215,13 @@
         <v>90</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3278,7 +3271,7 @@
         <v>78</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>76</v>
@@ -3290,7 +3283,7 @@
         <v>100</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>78</v>
@@ -3302,7 +3295,7 @@
         <v>78</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>78</v>
@@ -3410,7 +3403,7 @@
         <v>100</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>78</v>
@@ -3422,7 +3415,7 @@
         <v>78</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>78</v>
@@ -3530,7 +3523,7 @@
         <v>100</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>78</v>
@@ -3542,7 +3535,7 @@
         <v>78</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>78</v>
@@ -3564,7 +3557,7 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s" s="2">
         <v>77</v>
@@ -3626,17 +3619,19 @@
         <v>78</v>
       </c>
       <c r="AB10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF10" t="s" s="2">
         <v>141</v>
-      </c>
-      <c r="AC10" s="2"/>
-      <c r="AD10" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE10" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AF10" t="s" s="2">
-        <v>142</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>76</v>
@@ -3648,7 +3643,7 @@
         <v>100</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>78</v>
@@ -3660,7 +3655,7 @@
         <v>78</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>78</v>
@@ -3671,26 +3666,24 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>7</v>
-      </c>
+        <v>142</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>78</v>
@@ -3699,16 +3692,16 @@
         <v>89</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3719,7 +3712,7 @@
         <v>78</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>78</v>
@@ -3734,13 +3727,13 @@
         <v>78</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>78</v>
+        <v>149</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>78</v>
@@ -3758,7 +3751,7 @@
         <v>78</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>142</v>
+        <v>150</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>76</v>
@@ -3770,7 +3763,7 @@
         <v>100</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>78</v>
@@ -3779,10 +3772,10 @@
         <v>78</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>78</v>
+        <v>151</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>78</v>
@@ -3793,10 +3786,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3819,16 +3812,16 @@
         <v>89</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3854,13 +3847,13 @@
         <v>78</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>78</v>
@@ -3878,7 +3871,7 @@
         <v>78</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>76</v>
@@ -3890,7 +3883,7 @@
         <v>100</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>78</v>
@@ -3899,10 +3892,10 @@
         <v>78</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>78</v>
@@ -3913,10 +3906,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3927,28 +3920,28 @@
         <v>76</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I13" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J13" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3974,13 +3967,13 @@
         <v>78</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>160</v>
+        <v>78</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>161</v>
+        <v>78</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>78</v>
@@ -3998,19 +3991,19 @@
         <v>78</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>78</v>
@@ -4019,10 +4012,10 @@
         <v>78</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>153</v>
+        <v>78</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>154</v>
+        <v>108</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>78</v>
@@ -4033,10 +4026,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4053,22 +4046,22 @@
         <v>78</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4094,13 +4087,13 @@
         <v>78</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>78</v>
+        <v>173</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>78</v>
@@ -4118,7 +4111,7 @@
         <v>78</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>76</v>
@@ -4130,7 +4123,7 @@
         <v>100</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>78</v>
@@ -4142,7 +4135,7 @@
         <v>78</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>78</v>
@@ -4153,14 +4146,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>78</v>
+        <v>176</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4179,16 +4172,16 @@
         <v>78</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4214,13 +4207,13 @@
         <v>78</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>174</v>
+        <v>78</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>78</v>
@@ -4238,7 +4231,7 @@
         <v>78</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>76</v>
@@ -4250,7 +4243,7 @@
         <v>100</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>78</v>
@@ -4262,7 +4255,7 @@
         <v>78</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>107</v>
+        <v>182</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>78</v>
@@ -4273,21 +4266,21 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>78</v>
@@ -4299,16 +4292,16 @@
         <v>78</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4358,19 +4351,19 @@
         <v>78</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>78</v>
@@ -4382,7 +4375,7 @@
         <v>78</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>184</v>
+        <v>102</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>78</v>
@@ -4393,14 +4386,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>186</v>
+        <v>110</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4419,16 +4412,16 @@
         <v>78</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>187</v>
+        <v>111</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>112</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4466,19 +4459,19 @@
         <v>78</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -4487,10 +4480,10 @@
         <v>77</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>78</v>
@@ -4502,7 +4495,7 @@
         <v>78</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>78</v>
@@ -4513,21 +4506,23 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>190</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>194</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>78</v>
@@ -4539,17 +4534,15 @@
         <v>78</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>78</v>
@@ -4586,19 +4579,19 @@
         <v>78</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE18" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4610,7 +4603,7 @@
         <v>100</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>78</v>
@@ -4622,7 +4615,7 @@
         <v>78</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>78</v>
@@ -4633,13 +4626,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>78</v>
@@ -4661,13 +4654,13 @@
         <v>78</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4718,7 +4711,7 @@
         <v>78</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4730,7 +4723,7 @@
         <v>100</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>78</v>
@@ -4742,7 +4735,7 @@
         <v>78</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>78</v>
@@ -4753,44 +4746,46 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I20" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>202</v>
+        <v>111</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>78</v>
       </c>
@@ -4826,19 +4821,19 @@
         <v>78</v>
       </c>
       <c r="AB20" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC20" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>76</v>
@@ -4850,7 +4845,7 @@
         <v>100</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>78</v>
@@ -4862,7 +4857,7 @@
         <v>78</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>78</v>
+        <v>102</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>78</v>
@@ -4873,14 +4868,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4893,25 +4888,23 @@
         <v>78</v>
       </c>
       <c r="I21" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="J21" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="J21" t="s" s="2">
-        <v>78</v>
-      </c>
       <c r="K21" t="s" s="2">
-        <v>110</v>
+        <v>209</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>113</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>78</v>
@@ -4948,19 +4941,19 @@
         <v>78</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>76</v>
@@ -4972,22 +4965,22 @@
         <v>100</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>78</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>101</v>
+        <v>215</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>78</v>
+        <v>216</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>78</v>
@@ -4995,14 +4988,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5021,17 +5014,19 @@
         <v>89</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>222</v>
+      </c>
       <c r="O22" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>78</v>
@@ -5080,7 +5075,7 @@
         <v>78</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -5092,22 +5087,22 @@
         <v>100</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>218</v>
+        <v>78</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>78</v>
@@ -5115,14 +5110,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5141,20 +5136,18 @@
         <v>89</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>225</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>78</v>
       </c>
@@ -5202,7 +5195,7 @@
         <v>78</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>76</v>
@@ -5214,19 +5207,19 @@
         <v>100</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>78</v>
@@ -5237,44 +5230,46 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>78</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J24" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>167</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="O24" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>78</v>
       </c>
@@ -5298,13 +5293,13 @@
         <v>78</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>78</v>
+        <v>243</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>78</v>
+        <v>244</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>78</v>
@@ -5322,34 +5317,34 @@
         <v>78</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>78</v>
+        <v>246</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>78</v>
+        <v>249</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>78</v>
@@ -5357,10 +5352,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5371,31 +5366,31 @@
         <v>88</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>89</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>78</v>
@@ -5420,58 +5415,56 @@
         <v>78</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>246</v>
+        <v>257</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>247</v>
+        <v>78</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>248</v>
+        <v>78</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>78</v>
@@ -5479,12 +5472,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C26" s="2"/>
+        <v>250</v>
+      </c>
+      <c r="C26" t="s" s="2">
+        <v>263</v>
+      </c>
       <c r="D26" t="s" s="2">
         <v>78</v>
       </c>
@@ -5493,7 +5488,7 @@
         <v>88</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>89</v>
@@ -5505,19 +5500,19 @@
         <v>78</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>255</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>78</v>
@@ -5542,29 +5537,31 @@
         <v>78</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
@@ -5576,7 +5573,7 @@
         <v>100</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>78</v>
@@ -5585,13 +5582,13 @@
         <v>78</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>262</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>78</v>
@@ -5602,23 +5599,21 @@
         <v>264</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="C27" t="s" s="2">
         <v>265</v>
       </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>78</v>
@@ -5627,20 +5622,16 @@
         <v>78</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>254</v>
+        <v>105</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>257</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>78</v>
       </c>
@@ -5664,13 +5655,13 @@
         <v>78</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>173</v>
+        <v>78</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>258</v>
+        <v>78</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>259</v>
+        <v>78</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>78</v>
@@ -5688,19 +5679,19 @@
         <v>78</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>252</v>
+        <v>107</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>78</v>
@@ -5709,13 +5700,13 @@
         <v>78</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>261</v>
+        <v>78</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>263</v>
+        <v>78</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>78</v>
@@ -5730,14 +5721,14 @@
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>78</v>
@@ -5749,15 +5740,17 @@
         <v>78</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>78</v>
@@ -5794,31 +5787,31 @@
         <v>78</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>78</v>
@@ -5830,7 +5823,7 @@
         <v>78</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>78</v>
@@ -5848,37 +5841,39 @@
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>78</v>
       </c>
@@ -5914,19 +5909,19 @@
         <v>78</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -5938,7 +5933,7 @@
         <v>100</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>78</v>
@@ -5947,10 +5942,10 @@
         <v>78</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>78</v>
@@ -5961,10 +5956,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5972,35 +5967,31 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G30" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="G30" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>78</v>
       </c>
@@ -6048,19 +6039,19 @@
         <v>78</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>78</v>
@@ -6069,10 +6060,10 @@
         <v>78</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>78</v>
@@ -6090,14 +6081,14 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>78</v>
@@ -6109,15 +6100,17 @@
         <v>78</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>78</v>
@@ -6154,31 +6147,31 @@
         <v>78</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>78</v>
@@ -6190,7 +6183,7 @@
         <v>78</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>78</v>
@@ -6208,43 +6201,45 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O32" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O32" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>78</v>
+        <v>287</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>78</v>
@@ -6274,31 +6269,31 @@
         <v>78</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>78</v>
@@ -6307,10 +6302,10 @@
         <v>78</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>78</v>
@@ -6321,10 +6316,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6332,13 +6327,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>78</v>
@@ -6347,26 +6342,24 @@
         <v>89</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>289</v>
+        <v>78</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>78</v>
@@ -6408,7 +6401,7 @@
         <v>78</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -6420,7 +6413,7 @@
         <v>100</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>78</v>
@@ -6429,10 +6422,10 @@
         <v>78</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>78</v>
@@ -6443,10 +6436,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6454,13 +6447,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>78</v>
@@ -6469,24 +6462,26 @@
         <v>89</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>78</v>
+        <v>305</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>78</v>
@@ -6528,7 +6523,7 @@
         <v>78</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6540,7 +6535,7 @@
         <v>100</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>78</v>
@@ -6549,10 +6544,10 @@
         <v>78</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>78</v>
@@ -6563,10 +6558,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6574,13 +6569,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>78</v>
@@ -6589,26 +6584,26 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N35" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O35" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>307</v>
+        <v>78</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>78</v>
@@ -6650,7 +6645,7 @@
         <v>78</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6662,7 +6657,7 @@
         <v>100</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>78</v>
@@ -6671,10 +6666,10 @@
         <v>78</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>78</v>
@@ -6685,10 +6680,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6711,19 +6706,19 @@
         <v>89</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>78</v>
@@ -6772,7 +6767,7 @@
         <v>78</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6784,7 +6779,7 @@
         <v>100</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>78</v>
@@ -6793,10 +6788,10 @@
         <v>78</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>78</v>
@@ -6807,10 +6802,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6833,19 +6828,19 @@
         <v>89</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>78</v>
@@ -6894,7 +6889,7 @@
         <v>78</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6906,7 +6901,7 @@
         <v>100</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>78</v>
@@ -6915,10 +6910,10 @@
         <v>78</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>78</v>
@@ -6929,24 +6924,24 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>78</v>
@@ -6955,19 +6950,19 @@
         <v>89</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>78</v>
@@ -6992,13 +6987,13 @@
         <v>78</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>78</v>
@@ -7016,10 +7011,10 @@
         <v>78</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>88</v>
@@ -7028,69 +7023,65 @@
         <v>100</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>78</v>
+        <v>344</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>78</v>
+        <v>345</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>78</v>
+        <v>349</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>339</v>
+        <v>78</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>340</v>
+        <v>105</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>78</v>
       </c>
@@ -7114,13 +7105,13 @@
         <v>78</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>344</v>
+        <v>78</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>345</v>
+        <v>78</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>78</v>
@@ -7138,56 +7129,56 @@
         <v>78</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>338</v>
+        <v>107</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>346</v>
+        <v>78</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>347</v>
+        <v>78</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>349</v>
+        <v>108</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>351</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>78</v>
@@ -7199,15 +7190,17 @@
         <v>78</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>78</v>
@@ -7244,31 +7237,31 @@
         <v>78</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>78</v>
@@ -7280,7 +7273,7 @@
         <v>78</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>78</v>
@@ -7291,14 +7284,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7314,21 +7307,23 @@
         <v>78</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O41" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O41" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P41" t="s" s="2">
         <v>78</v>
       </c>
@@ -7337,7 +7332,7 @@
         <v>78</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>78</v>
+        <v>353</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>78</v>
@@ -7364,19 +7359,19 @@
         <v>78</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -7388,7 +7383,7 @@
         <v>100</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>78</v>
@@ -7397,10 +7392,10 @@
         <v>78</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>78</v>
@@ -7425,7 +7420,7 @@
         <v>76</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>78</v>
@@ -7437,19 +7432,19 @@
         <v>89</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>272</v>
+        <v>329</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>273</v>
+        <v>330</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>274</v>
+        <v>331</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>275</v>
+        <v>332</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>78</v>
@@ -7459,7 +7454,7 @@
         <v>78</v>
       </c>
       <c r="S42" t="s" s="2">
-        <v>355</v>
+        <v>78</v>
       </c>
       <c r="T42" t="s" s="2">
         <v>78</v>
@@ -7498,19 +7493,19 @@
         <v>78</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>276</v>
+        <v>333</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>78</v>
@@ -7519,10 +7514,10 @@
         <v>78</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>277</v>
+        <v>334</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>278</v>
+        <v>335</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>78</v>
@@ -7533,10 +7528,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7544,13 +7539,13 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>78</v>
@@ -7559,19 +7554,19 @@
         <v>89</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>103</v>
+        <v>356</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>331</v>
+        <v>357</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>333</v>
+        <v>359</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>334</v>
+        <v>360</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>78</v>
@@ -7620,7 +7615,7 @@
         <v>78</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>355</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7632,22 +7627,22 @@
         <v>100</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>78</v>
+        <v>361</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>336</v>
+        <v>362</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>78</v>
+        <v>364</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>78</v>
@@ -7655,10 +7650,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7666,13 +7661,13 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>78</v>
@@ -7681,20 +7676,18 @@
         <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>362</v>
-      </c>
+        <v>369</v>
+      </c>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>78</v>
       </c>
@@ -7742,34 +7735,34 @@
         <v>78</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>363</v>
+        <v>78</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM44" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AO44" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>366</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>78</v>
@@ -7777,21 +7770,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>78</v>
+        <v>372</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>78</v>
@@ -7803,18 +7796,20 @@
         <v>89</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="O45" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P45" t="s" s="2">
         <v>78</v>
       </c>
@@ -7862,34 +7857,34 @@
         <v>78</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>78</v>
+        <v>378</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>348</v>
+        <v>379</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>78</v>
@@ -7897,24 +7892,24 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>78</v>
@@ -7923,19 +7918,19 @@
         <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>78</v>
@@ -7984,7 +7979,7 @@
         <v>78</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7993,25 +7988,25 @@
         <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>100</v>
+        <v>389</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>226</v>
+        <v>390</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>78</v>
@@ -8019,24 +8014,24 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>385</v>
+        <v>78</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>78</v>
@@ -8045,20 +8040,18 @@
         <v>89</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>386</v>
+        <v>126</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>78</v>
       </c>
@@ -8106,7 +8099,7 @@
         <v>78</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -8115,25 +8108,25 @@
         <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>391</v>
+        <v>100</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>392</v>
+        <v>101</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>393</v>
+        <v>78</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>78</v>
@@ -8141,10 +8134,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8155,7 +8148,7 @@
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>78</v>
@@ -8167,18 +8160,20 @@
         <v>89</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>126</v>
+        <v>403</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>222</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>406</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>78</v>
       </c>
@@ -8226,34 +8221,34 @@
         <v>78</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>78</v>
+        <v>407</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>78</v>
@@ -8261,10 +8256,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8275,10 +8270,10 @@
         <v>76</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>78</v>
@@ -8287,19 +8282,19 @@
         <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>224</v>
+        <v>414</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>78</v>
@@ -8336,59 +8331,59 @@
         <v>78</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC49" t="s" s="2">
-        <v>78</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="AC49" s="2"/>
       <c r="AD49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>78</v>
+        <v>417</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>100</v>
+        <v>418</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>226</v>
+        <v>101</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>409</v>
+        <v>78</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>78</v>
+        <v>419</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>412</v>
+        <v>78</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C50" s="2"/>
+        <v>411</v>
+      </c>
+      <c r="C50" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="D50" t="s" s="2">
         <v>78</v>
       </c>
@@ -8409,19 +8404,19 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>415</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>78</v>
@@ -8431,7 +8426,7 @@
         <v>78</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>78</v>
+        <v>425</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>78</v>
@@ -8458,17 +8453,19 @@
         <v>78</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AC50" s="2"/>
+        <v>78</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>78</v>
+      </c>
       <c r="AD50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>419</v>
+        <v>78</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8477,40 +8474,38 @@
         <v>88</v>
       </c>
       <c r="AI50" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AJ50" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AP50" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP50" t="s" s="2">
-        <v>424</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C51" t="s" s="2">
-        <v>426</v>
-      </c>
+        <v>427</v>
+      </c>
+      <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8522,29 +8517,25 @@
         <v>88</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>414</v>
+        <v>104</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>415</v>
+        <v>105</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>417</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>78</v>
       </c>
@@ -8553,7 +8544,7 @@
         <v>78</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>427</v>
+        <v>78</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>78</v>
@@ -8592,7 +8583,7 @@
         <v>78</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>413</v>
+        <v>107</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8601,28 +8592,28 @@
         <v>88</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>420</v>
+        <v>78</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>421</v>
+        <v>78</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>422</v>
+        <v>78</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>423</v>
+        <v>108</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
     </row>
     <row r="52" hidden="true">
@@ -8634,14 +8625,14 @@
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>78</v>
@@ -8653,15 +8644,17 @@
         <v>78</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>78</v>
@@ -8698,31 +8691,31 @@
         <v>78</v>
       </c>
       <c r="AB52" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC52" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>78</v>
@@ -8734,7 +8727,7 @@
         <v>78</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>78</v>
@@ -8752,14 +8745,14 @@
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>78</v>
@@ -8768,21 +8761,23 @@
         <v>78</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>110</v>
+        <v>432</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>111</v>
+        <v>433</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>112</v>
+        <v>434</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>78</v>
       </c>
@@ -8818,31 +8813,31 @@
         <v>78</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>117</v>
+        <v>437</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>78</v>
@@ -8851,10 +8846,10 @@
         <v>78</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>78</v>
+        <v>438</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>101</v>
+        <v>439</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>78</v>
@@ -8865,10 +8860,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8885,30 +8880,32 @@
         <v>78</v>
       </c>
       <c r="I54" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J54" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>434</v>
+        <v>167</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>436</v>
+        <v>443</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>437</v>
+        <v>303</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q54" s="2"/>
+      <c r="Q54" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="R54" t="s" s="2">
         <v>78</v>
       </c>
@@ -8928,13 +8925,13 @@
         <v>78</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>78</v>
+        <v>242</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>78</v>
+        <v>446</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>78</v>
+        <v>447</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>78</v>
@@ -8952,7 +8949,7 @@
         <v>78</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8964,7 +8961,7 @@
         <v>100</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>78</v>
@@ -8973,10 +8970,10 @@
         <v>78</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>78</v>
@@ -8987,10 +8984,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8998,7 +8995,7 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>88</v>
@@ -9007,37 +9004,35 @@
         <v>78</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J55" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>78</v>
       </c>
-      <c r="Q55" t="s" s="2">
-        <v>447</v>
-      </c>
+      <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="S55" t="s" s="2">
-        <v>78</v>
+        <v>456</v>
       </c>
       <c r="T55" t="s" s="2">
         <v>78</v>
@@ -9052,13 +9047,13 @@
         <v>78</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>448</v>
+        <v>78</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>449</v>
+        <v>78</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>78</v>
@@ -9076,7 +9071,7 @@
         <v>78</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>450</v>
+        <v>457</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -9088,7 +9083,7 @@
         <v>100</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>78</v>
@@ -9097,10 +9092,10 @@
         <v>78</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>451</v>
+        <v>458</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>78</v>
@@ -9111,10 +9106,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>454</v>
+        <v>461</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9137,19 +9132,19 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>455</v>
+        <v>462</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>456</v>
+        <v>463</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>305</v>
+        <v>464</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>78</v>
@@ -9159,7 +9154,7 @@
         <v>78</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>458</v>
+        <v>78</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>78</v>
@@ -9198,7 +9193,7 @@
         <v>78</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -9207,10 +9202,10 @@
         <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>100</v>
+        <v>467</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>78</v>
@@ -9219,10 +9214,10 @@
         <v>78</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>78</v>
@@ -9233,10 +9228,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9259,19 +9254,19 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>132</v>
+        <v>167</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>466</v>
+        <v>473</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>78</v>
@@ -9320,7 +9315,7 @@
         <v>78</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -9329,10 +9324,10 @@
         <v>88</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>469</v>
+        <v>100</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>78</v>
@@ -9341,10 +9336,10 @@
         <v>78</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>78</v>
@@ -9355,10 +9350,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9366,34 +9361,34 @@
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>78</v>
@@ -9418,13 +9413,13 @@
         <v>78</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>78</v>
+        <v>482</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>78</v>
+        <v>483</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>78</v>
@@ -9451,10 +9446,10 @@
         <v>88</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>100</v>
+        <v>484</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>78</v>
@@ -9463,10 +9458,10 @@
         <v>78</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>460</v>
+        <v>102</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>78</v>
@@ -9477,10 +9472,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9494,7 +9489,7 @@
         <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I59" t="s" s="2">
         <v>78</v>
@@ -9503,20 +9498,16 @@
         <v>78</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>480</v>
+        <v>105</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>482</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>483</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>78</v>
       </c>
@@ -9540,13 +9531,13 @@
         <v>78</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>484</v>
+        <v>78</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>485</v>
+        <v>78</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>78</v>
@@ -9564,7 +9555,7 @@
         <v>78</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>479</v>
+        <v>107</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9573,10 +9564,10 @@
         <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>486</v>
+        <v>78</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>78</v>
@@ -9585,10 +9576,10 @@
         <v>78</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>487</v>
+        <v>108</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>78</v>
@@ -9599,21 +9590,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>78</v>
@@ -9625,15 +9616,17 @@
         <v>78</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>78</v>
@@ -9670,31 +9663,31 @@
         <v>78</v>
       </c>
       <c r="AB60" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC60" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>78</v>
@@ -9706,7 +9699,7 @@
         <v>78</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>78</v>
@@ -9717,14 +9710,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9740,21 +9733,23 @@
         <v>78</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O61" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>78</v>
       </c>
@@ -9790,19 +9785,19 @@
         <v>78</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9814,7 +9809,7 @@
         <v>100</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>78</v>
@@ -9823,10 +9818,10 @@
         <v>78</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>78</v>
@@ -9837,10 +9832,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9851,7 +9846,7 @@
         <v>76</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>78</v>
@@ -9860,23 +9855,19 @@
         <v>78</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>78</v>
       </c>
@@ -9924,19 +9915,19 @@
         <v>78</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>78</v>
@@ -9945,10 +9936,10 @@
         <v>78</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>78</v>
@@ -9959,21 +9950,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>78</v>
@@ -9985,15 +9976,17 @@
         <v>78</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>78</v>
@@ -10030,31 +10023,31 @@
         <v>78</v>
       </c>
       <c r="AB63" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC63" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE63" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>78</v>
@@ -10066,7 +10059,7 @@
         <v>78</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>78</v>
@@ -10077,21 +10070,21 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>78</v>
@@ -10100,21 +10093,23 @@
         <v>78</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>78</v>
       </c>
@@ -10150,31 +10145,31 @@
         <v>78</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>78</v>
@@ -10183,10 +10178,10 @@
         <v>78</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>78</v>
@@ -10197,10 +10192,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10208,7 +10203,7 @@
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s" s="2">
         <v>88</v>
@@ -10223,20 +10218,18 @@
         <v>89</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>78</v>
       </c>
@@ -10284,7 +10277,7 @@
         <v>78</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -10296,7 +10289,7 @@
         <v>100</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>78</v>
@@ -10305,10 +10298,10 @@
         <v>78</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>78</v>
@@ -10319,10 +10312,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10330,7 +10323,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>88</v>
@@ -10345,18 +10338,20 @@
         <v>89</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O66" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>78</v>
       </c>
@@ -10404,7 +10399,7 @@
         <v>78</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -10416,7 +10411,7 @@
         <v>100</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>78</v>
@@ -10425,10 +10420,10 @@
         <v>78</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>78</v>
@@ -10439,10 +10434,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10450,7 +10445,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>88</v>
@@ -10465,19 +10460,19 @@
         <v>89</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M67" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O67" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>78</v>
@@ -10526,7 +10521,7 @@
         <v>78</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10538,7 +10533,7 @@
         <v>100</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>78</v>
@@ -10547,10 +10542,10 @@
         <v>78</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>78</v>
@@ -10561,10 +10556,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10587,19 +10582,19 @@
         <v>89</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>78</v>
@@ -10648,7 +10643,7 @@
         <v>78</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10660,7 +10655,7 @@
         <v>100</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>78</v>
@@ -10669,10 +10664,10 @@
         <v>78</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>78</v>
@@ -10683,10 +10678,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10709,19 +10704,19 @@
         <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>78</v>
@@ -10770,7 +10765,7 @@
         <v>78</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10782,7 +10777,7 @@
         <v>100</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>78</v>
@@ -10791,10 +10786,10 @@
         <v>78</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>78</v>
@@ -10805,21 +10800,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>78</v>
+        <v>498</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>78</v>
@@ -10828,22 +10823,22 @@
         <v>78</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>103</v>
+        <v>251</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>331</v>
+        <v>499</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>332</v>
+        <v>500</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>333</v>
+        <v>501</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>334</v>
+        <v>502</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>78</v>
@@ -10868,13 +10863,13 @@
         <v>78</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>78</v>
+        <v>503</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>78</v>
+        <v>504</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>78</v>
@@ -10892,49 +10887,49 @@
         <v>78</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>335</v>
+        <v>497</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>78</v>
+        <v>505</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>336</v>
+        <v>506</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>337</v>
+        <v>507</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>78</v>
+        <v>508</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>500</v>
+        <v>78</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10953,19 +10948,19 @@
         <v>78</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>253</v>
+        <v>510</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>501</v>
+        <v>511</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>503</v>
+        <v>513</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>504</v>
+        <v>514</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>78</v>
@@ -10990,13 +10985,13 @@
         <v>78</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>506</v>
+        <v>78</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>78</v>
@@ -11014,7 +11009,7 @@
         <v>78</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>499</v>
+        <v>509</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -11026,33 +11021,33 @@
         <v>100</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>507</v>
+        <v>78</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>510</v>
+        <v>78</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11063,7 +11058,7 @@
         <v>76</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>78</v>
@@ -11075,20 +11070,18 @@
         <v>78</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>512</v>
+        <v>251</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>514</v>
+        <v>519</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>78</v>
       </c>
@@ -11112,13 +11105,13 @@
         <v>78</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>78</v>
+        <v>157</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>78</v>
+        <v>521</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>78</v>
+        <v>522</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>78</v>
@@ -11136,45 +11129,45 @@
         <v>78</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>78</v>
+        <v>523</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>78</v>
+        <v>526</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11197,18 +11190,20 @@
         <v>78</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>520</v>
+        <v>528</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>521</v>
+        <v>529</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>78</v>
       </c>
@@ -11232,13 +11227,13 @@
         <v>78</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>159</v>
+        <v>242</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>78</v>
@@ -11256,7 +11251,7 @@
         <v>78</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>519</v>
+        <v>527</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>76</v>
@@ -11268,33 +11263,33 @@
         <v>100</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>525</v>
+        <v>78</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>526</v>
+        <v>533</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>528</v>
+        <v>78</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11317,20 +11312,16 @@
         <v>78</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>253</v>
+        <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>530</v>
+        <v>105</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>78</v>
       </c>
@@ -11354,13 +11345,13 @@
         <v>78</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>244</v>
+        <v>78</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>534</v>
+        <v>78</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>78</v>
@@ -11378,7 +11369,7 @@
         <v>78</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>529</v>
+        <v>107</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -11387,10 +11378,10 @@
         <v>88</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>78</v>
@@ -11399,10 +11390,10 @@
         <v>78</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>535</v>
+        <v>78</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>536</v>
+        <v>108</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>78</v>
@@ -11413,21 +11404,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>78</v>
@@ -11439,15 +11430,17 @@
         <v>78</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>78</v>
@@ -11484,31 +11477,31 @@
         <v>78</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>78</v>
@@ -11520,7 +11513,7 @@
         <v>78</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>78</v>
@@ -11531,14 +11524,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11554,21 +11547,23 @@
         <v>78</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>111</v>
+        <v>270</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>112</v>
+        <v>271</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>272</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>273</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>78</v>
       </c>
@@ -11604,19 +11599,19 @@
         <v>78</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>117</v>
+        <v>274</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11628,7 +11623,7 @@
         <v>100</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>78</v>
@@ -11637,10 +11632,10 @@
         <v>78</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>78</v>
+        <v>275</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>101</v>
+        <v>276</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>78</v>
@@ -11651,10 +11646,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11665,7 +11660,7 @@
         <v>76</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>78</v>
@@ -11674,23 +11669,19 @@
         <v>78</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>145</v>
+        <v>104</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>272</v>
+        <v>105</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>273</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>78</v>
       </c>
@@ -11738,19 +11729,19 @@
         <v>78</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>276</v>
+        <v>107</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>78</v>
@@ -11759,10 +11750,10 @@
         <v>78</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>277</v>
+        <v>78</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>278</v>
+        <v>108</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>78</v>
@@ -11773,21 +11764,21 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>78</v>
@@ -11799,15 +11790,17 @@
         <v>78</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>78</v>
@@ -11844,31 +11837,31 @@
         <v>78</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE78" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>78</v>
@@ -11880,7 +11873,7 @@
         <v>78</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>78</v>
@@ -11891,21 +11884,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>78</v>
@@ -11914,21 +11907,23 @@
         <v>78</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>111</v>
+        <v>283</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>112</v>
+        <v>284</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>285</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>286</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>78</v>
       </c>
@@ -11964,31 +11959,31 @@
         <v>78</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>117</v>
+        <v>288</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>78</v>
@@ -11997,10 +11992,10 @@
         <v>78</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>78</v>
+        <v>289</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>101</v>
+        <v>290</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>78</v>
@@ -12011,10 +12006,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12022,7 +12017,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>88</v>
@@ -12037,20 +12032,18 @@
         <v>89</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>132</v>
+        <v>104</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>288</v>
-      </c>
+        <v>295</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>78</v>
       </c>
@@ -12098,7 +12091,7 @@
         <v>78</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -12110,7 +12103,7 @@
         <v>100</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>78</v>
@@ -12119,10 +12112,10 @@
         <v>78</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>78</v>
@@ -12133,10 +12126,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12144,7 +12137,7 @@
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G81" t="s" s="2">
         <v>88</v>
@@ -12159,18 +12152,20 @@
         <v>89</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>103</v>
+        <v>167</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>303</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>304</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>78</v>
       </c>
@@ -12218,7 +12213,7 @@
         <v>78</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -12230,7 +12225,7 @@
         <v>100</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>78</v>
@@ -12239,10 +12234,10 @@
         <v>78</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>78</v>
@@ -12253,10 +12248,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12264,7 +12259,7 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G82" t="s" s="2">
         <v>88</v>
@@ -12279,19 +12274,19 @@
         <v>89</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="L82" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="N82" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="M82" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>305</v>
-      </c>
       <c r="O82" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>78</v>
@@ -12340,7 +12335,7 @@
         <v>78</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>76</v>
@@ -12352,7 +12347,7 @@
         <v>100</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>78</v>
@@ -12361,10 +12356,10 @@
         <v>78</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>78</v>
@@ -12375,10 +12370,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12401,19 +12396,19 @@
         <v>89</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>103</v>
+        <v>319</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>78</v>
@@ -12462,7 +12457,7 @@
         <v>78</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>76</v>
@@ -12474,7 +12469,7 @@
         <v>100</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>78</v>
@@ -12483,10 +12478,10 @@
         <v>78</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>78</v>
@@ -12497,10 +12492,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12523,19 +12518,19 @@
         <v>89</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>321</v>
+        <v>104</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>78</v>
@@ -12584,7 +12579,7 @@
         <v>78</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12596,7 +12591,7 @@
         <v>100</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>78</v>
@@ -12605,10 +12600,10 @@
         <v>78</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>78</v>
@@ -12619,10 +12614,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12642,23 +12637,21 @@
         <v>78</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>103</v>
+        <v>547</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>331</v>
+        <v>548</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>332</v>
+        <v>549</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>334</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>78</v>
       </c>
@@ -12706,7 +12699,7 @@
         <v>78</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>335</v>
+        <v>546</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -12718,33 +12711,33 @@
         <v>100</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>78</v>
+        <v>551</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>336</v>
+        <v>552</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>337</v>
+        <v>553</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>78</v>
+        <v>554</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12767,16 +12760,16 @@
         <v>78</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>549</v>
+        <v>556</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>550</v>
+        <v>557</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>551</v>
+        <v>558</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>552</v>
+        <v>559</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -12826,7 +12819,7 @@
         <v>78</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12838,33 +12831,33 @@
         <v>100</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>554</v>
+        <v>561</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>555</v>
+        <v>562</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>556</v>
+        <v>563</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12875,7 +12868,7 @@
         <v>76</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>78</v>
@@ -12887,18 +12880,20 @@
         <v>78</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>558</v>
+        <v>565</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>559</v>
+        <v>566</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>78</v>
       </c>
@@ -12946,45 +12941,45 @@
         <v>78</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>557</v>
+        <v>564</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>226</v>
+        <v>570</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>562</v>
+        <v>78</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>563</v>
+        <v>571</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>564</v>
+        <v>572</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>565</v>
+        <v>78</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>566</v>
+        <v>573</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12995,7 +12990,7 @@
         <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>78</v>
@@ -13007,20 +13002,16 @@
         <v>78</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>567</v>
+        <v>104</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>568</v>
+        <v>105</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>571</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>78</v>
       </c>
@@ -13068,19 +13059,19 @@
         <v>78</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>566</v>
+        <v>107</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>572</v>
+        <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>78</v>
@@ -13089,10 +13080,10 @@
         <v>78</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>573</v>
+        <v>78</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>574</v>
+        <v>108</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>78</v>
@@ -13103,21 +13094,21 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>78</v>
@@ -13129,15 +13120,17 @@
         <v>78</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>78</v>
@@ -13174,31 +13167,31 @@
         <v>78</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>78</v>
@@ -13210,7 +13203,7 @@
         <v>78</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>78</v>
@@ -13221,14 +13214,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>109</v>
+        <v>576</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -13241,24 +13234,26 @@
         <v>78</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>111</v>
+        <v>577</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>78</v>
       </c>
@@ -13294,19 +13289,19 @@
         <v>78</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>117</v>
+        <v>579</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -13318,7 +13313,7 @@
         <v>100</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>78</v>
@@ -13330,7 +13325,7 @@
         <v>78</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>78</v>
@@ -13341,46 +13336,44 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>578</v>
+        <v>78</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>110</v>
+        <v>581</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>208</v>
-      </c>
+        <v>584</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>78</v>
       </c>
@@ -13428,19 +13421,19 @@
         <v>78</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>100</v>
+        <v>585</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>118</v>
+        <v>586</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>78</v>
@@ -13449,10 +13442,10 @@
         <v>78</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>78</v>
+        <v>587</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>101</v>
+        <v>588</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>78</v>
@@ -13463,10 +13456,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13489,16 +13482,16 @@
         <v>78</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N92" t="s" s="2">
         <v>584</v>
-      </c>
-      <c r="M92" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13548,7 +13541,7 @@
         <v>78</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -13557,22 +13550,22 @@
         <v>88</v>
       </c>
       <c r="AI92" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>587</v>
       </c>
-      <c r="AJ92" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="AK92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL92" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM92" t="s" s="2">
-        <v>589</v>
-      </c>
       <c r="AN92" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>78</v>
@@ -13583,10 +13576,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13609,18 +13602,20 @@
         <v>78</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>583</v>
+        <v>251</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="O93" s="2"/>
+        <v>596</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>597</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>78</v>
       </c>
@@ -13644,13 +13639,13 @@
         <v>78</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>78</v>
+        <v>171</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>78</v>
+        <v>598</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>78</v>
+        <v>599</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>78</v>
@@ -13668,7 +13663,7 @@
         <v>78</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -13677,22 +13672,22 @@
         <v>88</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>587</v>
+        <v>100</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>588</v>
+        <v>101</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>78</v>
+        <v>600</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>594</v>
+        <v>507</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>78</v>
@@ -13703,10 +13698,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13717,7 +13712,7 @@
         <v>76</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>78</v>
@@ -13729,19 +13724,19 @@
         <v>78</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>596</v>
+        <v>603</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>597</v>
+        <v>604</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>598</v>
+        <v>605</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>599</v>
+        <v>606</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>78</v>
@@ -13766,13 +13761,13 @@
         <v>78</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>600</v>
+        <v>607</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>78</v>
@@ -13790,31 +13785,31 @@
         <v>78</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>595</v>
+        <v>602</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>78</v>
@@ -13825,10 +13820,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13839,7 +13834,7 @@
         <v>76</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>78</v>
@@ -13851,19 +13846,19 @@
         <v>78</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>253</v>
+        <v>610</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>605</v>
+        <v>611</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>606</v>
+        <v>612</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>607</v>
+        <v>613</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>608</v>
+        <v>614</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>78</v>
@@ -13888,55 +13883,55 @@
         <v>78</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>159</v>
+        <v>78</v>
       </c>
       <c r="Y95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AF95" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="Z95" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>604</v>
-      </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>124</v>
+        <v>615</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>602</v>
+        <v>78</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>603</v>
+        <v>616</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>509</v>
+        <v>617</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>78</v>
@@ -13947,10 +13942,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13973,20 +13968,18 @@
         <v>78</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>612</v>
+        <v>104</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>613</v>
+        <v>619</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>614</v>
+        <v>620</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
         <v>78</v>
       </c>
@@ -14034,7 +14027,7 @@
         <v>78</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>611</v>
+        <v>618</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -14046,7 +14039,7 @@
         <v>100</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>617</v>
+        <v>101</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>78</v>
@@ -14055,10 +14048,10 @@
         <v>78</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>618</v>
+        <v>587</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>78</v>
@@ -14069,10 +14062,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14083,7 +14076,7 @@
         <v>76</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>78</v>
@@ -14092,19 +14085,19 @@
         <v>78</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>103</v>
+        <v>623</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>305</v>
+        <v>626</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14154,19 +14147,19 @@
         <v>78</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI97" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>124</v>
+        <v>224</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>78</v>
@@ -14175,10 +14168,10 @@
         <v>78</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>589</v>
+        <v>627</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>623</v>
+        <v>628</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>78</v>
@@ -14189,10 +14182,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14215,16 +14208,16 @@
         <v>89</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>626</v>
+        <v>631</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>627</v>
+        <v>632</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>628</v>
+        <v>633</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -14274,7 +14267,7 @@
         <v>78</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -14286,7 +14279,7 @@
         <v>100</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>78</v>
@@ -14295,10 +14288,10 @@
         <v>78</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>78</v>
@@ -14309,10 +14302,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14326,7 +14319,7 @@
         <v>77</v>
       </c>
       <c r="H99" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I99" t="s" s="2">
         <v>78</v>
@@ -14335,18 +14328,20 @@
         <v>89</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>632</v>
+        <v>565</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="O99" s="2"/>
+        <v>637</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>638</v>
+      </c>
       <c r="P99" t="s" s="2">
         <v>78</v>
       </c>
@@ -14394,7 +14389,7 @@
         <v>78</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -14406,7 +14401,7 @@
         <v>100</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>226</v>
+        <v>639</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>78</v>
@@ -14415,10 +14410,10 @@
         <v>78</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>78</v>
@@ -14429,10 +14424,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>637</v>
+        <v>642</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14443,32 +14438,28 @@
         <v>76</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>78</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>567</v>
+        <v>104</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>638</v>
+        <v>105</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>640</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>78</v>
       </c>
@@ -14516,19 +14507,19 @@
         <v>78</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>637</v>
+        <v>107</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH100" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>641</v>
+        <v>78</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>78</v>
@@ -14537,10 +14528,10 @@
         <v>78</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>642</v>
+        <v>78</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>643</v>
+        <v>108</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>78</v>
@@ -14551,21 +14542,21 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>78</v>
+        <v>110</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H101" t="s" s="2">
         <v>78</v>
@@ -14577,15 +14568,17 @@
         <v>78</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>78</v>
@@ -14622,31 +14615,31 @@
         <v>78</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="AC101" t="s" s="2">
-        <v>78</v>
+        <v>116</v>
       </c>
       <c r="AD101" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE101" t="s" s="2">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>78</v>
+        <v>119</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>78</v>
@@ -14658,7 +14651,7 @@
         <v>78</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>78</v>
@@ -14669,14 +14662,14 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>109</v>
+        <v>576</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
@@ -14689,24 +14682,26 @@
         <v>78</v>
       </c>
       <c r="I102" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>111</v>
+        <v>577</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="O102" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>206</v>
+      </c>
       <c r="P102" t="s" s="2">
         <v>78</v>
       </c>
@@ -14742,19 +14737,19 @@
         <v>78</v>
       </c>
       <c r="AB102" t="s" s="2">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="AC102" t="s" s="2">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="AD102" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AE102" t="s" s="2">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>117</v>
+        <v>579</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -14766,7 +14761,7 @@
         <v>100</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>78</v>
@@ -14778,7 +14773,7 @@
         <v>78</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>78</v>
@@ -14789,45 +14784,45 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>578</v>
+        <v>78</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="J103" t="s" s="2">
         <v>89</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>110</v>
+        <v>251</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>579</v>
+        <v>646</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>580</v>
+        <v>647</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>113</v>
+        <v>648</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>208</v>
+        <v>649</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>78</v>
@@ -14852,13 +14847,13 @@
         <v>78</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>78</v>
+        <v>147</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>78</v>
+        <v>343</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>78</v>
@@ -14876,34 +14871,34 @@
         <v>78</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>581</v>
+        <v>645</v>
       </c>
       <c r="AG103" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>100</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>78</v>
+        <v>650</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>78</v>
+        <v>346</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>101</v>
+        <v>347</v>
       </c>
       <c r="AO103" t="s" s="2">
-        <v>78</v>
+        <v>348</v>
       </c>
       <c r="AP103" t="s" s="2">
         <v>78</v>
@@ -14911,10 +14906,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14922,7 +14917,7 @@
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>88</v>
@@ -14937,19 +14932,19 @@
         <v>89</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>253</v>
+        <v>652</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>648</v>
+        <v>653</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>651</v>
+        <v>415</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>78</v>
@@ -14974,13 +14969,13 @@
         <v>78</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>149</v>
+        <v>242</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>344</v>
+        <v>656</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>345</v>
+        <v>657</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>78</v>
@@ -14998,45 +14993,45 @@
         <v>78</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>88</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>100</v>
+        <v>658</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>348</v>
+        <v>420</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>349</v>
+        <v>421</v>
       </c>
       <c r="AO104" t="s" s="2">
-        <v>350</v>
+        <v>78</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>78</v>
+        <v>422</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -15056,22 +15051,22 @@
         <v>78</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>654</v>
+        <v>251</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>655</v>
+        <v>661</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>656</v>
+        <v>662</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>657</v>
+        <v>663</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>417</v>
+        <v>481</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>78</v>
@@ -15096,13 +15091,13 @@
         <v>78</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>244</v>
+        <v>147</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>658</v>
+        <v>482</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>659</v>
+        <v>483</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>78</v>
@@ -15120,7 +15115,7 @@
         <v>78</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -15129,50 +15124,50 @@
         <v>88</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>661</v>
+        <v>78</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>422</v>
+        <v>102</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>423</v>
+        <v>485</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>424</v>
+        <v>78</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>78</v>
+        <v>498</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H106" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I106" t="s" s="2">
         <v>78</v>
@@ -15181,19 +15176,19 @@
         <v>78</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>663</v>
+        <v>499</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>664</v>
+        <v>500</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>665</v>
+        <v>501</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>483</v>
+        <v>502</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>78</v>
@@ -15218,13 +15213,13 @@
         <v>78</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="Y106" t="s" s="2">
-        <v>484</v>
+        <v>503</v>
       </c>
       <c r="Z106" t="s" s="2">
-        <v>485</v>
+        <v>504</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>78</v>
@@ -15242,49 +15237,49 @@
         <v>78</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>666</v>
+        <v>100</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>78</v>
+        <v>505</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>101</v>
+        <v>506</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>487</v>
+        <v>507</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP106" t="s" s="2">
-        <v>78</v>
+        <v>508</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>500</v>
+        <v>78</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -15303,19 +15298,19 @@
         <v>78</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>253</v>
+        <v>79</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>501</v>
+        <v>667</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>502</v>
+        <v>668</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>503</v>
+        <v>568</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>504</v>
+        <v>569</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>78</v>
@@ -15340,13 +15335,13 @@
         <v>78</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>149</v>
+        <v>78</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>505</v>
+        <v>78</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>506</v>
+        <v>78</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>78</v>
@@ -15364,7 +15359,7 @@
         <v>78</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -15373,154 +15368,32 @@
         <v>77</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>124</v>
+        <v>78</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>507</v>
+        <v>78</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>508</v>
+        <v>571</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>509</v>
+        <v>572</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AP107" t="s" s="2">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="P108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AP108" t="s" s="2">
         <v>78</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP108">
+  <autoFilter ref="A1:AP107">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15530,7 +15403,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI107">
+  <conditionalFormatting sqref="A2:AI106">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T08:27:54+00:00</t>
+    <t>2023-04-26T14:43:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-26T14:43:04+00:00</t>
+    <t>2023-04-27T16:49:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-27T16:49:23+00:00</t>
+    <t>2023-05-02T12:59:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T12:59:07+00:00</t>
+    <t>2023-05-02T13:06:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T13:06:55+00:00</t>
+    <t>2023-05-02T14:05:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:33:57+00:00</t>
+    <t>2023-07-18T09:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:12+00:00</t>
+    <t>2023-07-18T09:34:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:34:49+00:00</t>
+    <t>2023-07-18T09:37:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4064" uniqueCount="616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4064" uniqueCount="617">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-07-18T09:37:51+00:00</t>
+    <t>2023-09-19T16:09:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -141,6 +141,10 @@
   </si>
   <si>
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}obs-7:If Observation.code is the same as an Observation.component.code then the value element associated with the code SHALL NOT be present {value.empty() or component.code.where(coding.intersect(%resource.code.coding).exists()).empty()}obs-6:dataAbsentReason SHALL only be present if Observation.value[x] is not present {dataAbsentReason.empty() or value.empty()}vs-2:If there is no component or hasMember element then either a value[x] or a data absent reason must be present. {(component.empty() and hasMember.empty()) implies (dataAbsentReason.exists() or value.exists())}</t>
   </si>
   <si>
     <t>Event</t>
@@ -2398,19 +2402,19 @@
         <v>36</v>
       </c>
       <c r="AJ1" t="s" s="2">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="AK1" t="s" s="2">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="AL1" t="s" s="2">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="AM1" t="s" s="2">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AN1" t="s" s="2">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="AO1" t="s" s="2">
         <v>36</v>
@@ -2421,10 +2425,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2435,7 +2439,7 @@
         <v>34</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>36</v>
@@ -2444,19 +2448,19 @@
         <v>36</v>
       </c>
       <c r="J2" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N2" t="s" s="2">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" t="s" s="2">
@@ -2506,13 +2510,13 @@
         <v>36</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>36</v>
@@ -2541,10 +2545,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2555,7 +2559,7 @@
         <v>34</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>36</v>
@@ -2564,16 +2568,16 @@
         <v>36</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -2624,19 +2628,19 @@
         <v>36</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI3" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ3" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK3" t="s" s="2">
         <v>36</v>
@@ -2648,7 +2652,7 @@
         <v>36</v>
       </c>
       <c r="AN3" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO3" t="s" s="2">
         <v>36</v>
@@ -2659,10 +2663,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2673,7 +2677,7 @@
         <v>34</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>36</v>
@@ -2685,13 +2689,13 @@
         <v>36</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2742,13 +2746,13 @@
         <v>36</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>36</v>
@@ -2766,7 +2770,7 @@
         <v>36</v>
       </c>
       <c r="AN4" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO4" t="s" s="2">
         <v>36</v>
@@ -2777,14 +2781,14 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
@@ -2803,16 +2807,16 @@
         <v>36</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2850,19 +2854,19 @@
         <v>36</v>
       </c>
       <c r="AB5" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC5" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD5" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE5" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>34</v>
@@ -2871,10 +2875,10 @@
         <v>35</v>
       </c>
       <c r="AI5" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>36</v>
@@ -2886,7 +2890,7 @@
         <v>36</v>
       </c>
       <c r="AN5" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO5" t="s" s="2">
         <v>36</v>
@@ -2897,10 +2901,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2911,7 +2915,7 @@
         <v>34</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>36</v>
@@ -2920,19 +2924,19 @@
         <v>36</v>
       </c>
       <c r="J6" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2982,19 +2986,19 @@
         <v>36</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI6" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>36</v>
@@ -3006,7 +3010,7 @@
         <v>36</v>
       </c>
       <c r="AN6" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO6" t="s" s="2">
         <v>36</v>
@@ -3017,10 +3021,10 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -3031,7 +3035,7 @@
         <v>34</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>36</v>
@@ -3040,19 +3044,19 @@
         <v>36</v>
       </c>
       <c r="J7" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -3102,19 +3106,19 @@
         <v>36</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>36</v>
@@ -3126,7 +3130,7 @@
         <v>36</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>36</v>
@@ -3137,10 +3141,10 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -3151,7 +3155,7 @@
         <v>34</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>36</v>
@@ -3160,19 +3164,19 @@
         <v>36</v>
       </c>
       <c r="J8" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -3222,19 +3226,19 @@
         <v>36</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>36</v>
@@ -3246,7 +3250,7 @@
         <v>36</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>36</v>
@@ -3257,10 +3261,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -3280,19 +3284,19 @@
         <v>36</v>
       </c>
       <c r="J9" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3342,7 +3346,7 @@
         <v>36</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>34</v>
@@ -3351,10 +3355,10 @@
         <v>35</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>36</v>
@@ -3366,7 +3370,7 @@
         <v>36</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>36</v>
@@ -3377,10 +3381,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3400,19 +3404,19 @@
         <v>36</v>
       </c>
       <c r="J10" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3438,13 +3442,13 @@
         <v>36</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>36</v>
@@ -3462,7 +3466,7 @@
         <v>36</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>34</v>
@@ -3471,10 +3475,10 @@
         <v>35</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>36</v>
@@ -3483,10 +3487,10 @@
         <v>36</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN10" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>36</v>
@@ -3497,10 +3501,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3520,19 +3524,19 @@
         <v>36</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3558,13 +3562,13 @@
         <v>36</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>36</v>
@@ -3582,7 +3586,7 @@
         <v>36</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>34</v>
@@ -3591,10 +3595,10 @@
         <v>35</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>36</v>
@@ -3603,10 +3607,10 @@
         <v>36</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>36</v>
@@ -3617,10 +3621,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3631,28 +3635,28 @@
         <v>34</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3702,19 +3706,19 @@
         <v>36</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>36</v>
@@ -3726,7 +3730,7 @@
         <v>36</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>36</v>
@@ -3737,10 +3741,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3751,7 +3755,7 @@
         <v>34</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>36</v>
@@ -3763,16 +3767,16 @@
         <v>36</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3798,13 +3802,13 @@
         <v>36</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>36</v>
@@ -3822,19 +3826,19 @@
         <v>36</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>36</v>
@@ -3846,7 +3850,7 @@
         <v>36</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>36</v>
@@ -3857,21 +3861,21 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>36</v>
@@ -3883,16 +3887,16 @@
         <v>36</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3942,19 +3946,19 @@
         <v>36</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>36</v>
@@ -3966,7 +3970,7 @@
         <v>36</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>36</v>
@@ -3977,14 +3981,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4003,16 +4007,16 @@
         <v>36</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4062,7 +4066,7 @@
         <v>36</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>34</v>
@@ -4086,7 +4090,7 @@
         <v>36</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>36</v>
@@ -4097,14 +4101,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4123,16 +4127,16 @@
         <v>36</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4170,19 +4174,19 @@
         <v>36</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC16" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD16" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>34</v>
@@ -4191,10 +4195,10 @@
         <v>35</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>36</v>
@@ -4206,7 +4210,7 @@
         <v>36</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>36</v>
@@ -4217,13 +4221,13 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>36</v>
@@ -4233,7 +4237,7 @@
         <v>34</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>36</v>
@@ -4245,13 +4249,13 @@
         <v>36</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4302,7 +4306,7 @@
         <v>36</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>34</v>
@@ -4311,10 +4315,10 @@
         <v>35</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>36</v>
@@ -4326,7 +4330,7 @@
         <v>36</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>36</v>
@@ -4337,13 +4341,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>36</v>
@@ -4353,7 +4357,7 @@
         <v>34</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>36</v>
@@ -4365,13 +4369,13 @@
         <v>36</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4422,7 +4426,7 @@
         <v>36</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>34</v>
@@ -4431,10 +4435,10 @@
         <v>35</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>36</v>
@@ -4457,14 +4461,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -4477,25 +4481,25 @@
         <v>36</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O19" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>36</v>
@@ -4532,19 +4536,19 @@
         <v>36</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>34</v>
@@ -4553,10 +4557,10 @@
         <v>35</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>36</v>
@@ -4568,7 +4572,7 @@
         <v>36</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>36</v>
@@ -4579,10 +4583,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4602,20 +4606,20 @@
         <v>36</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>36</v>
@@ -4664,7 +4668,7 @@
         <v>36</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>34</v>
@@ -4673,25 +4677,25 @@
         <v>35</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>36</v>
@@ -4699,14 +4703,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4722,22 +4726,22 @@
         <v>36</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>36</v>
@@ -4786,7 +4790,7 @@
         <v>36</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>34</v>
@@ -4795,22 +4799,22 @@
         <v>35</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>36</v>
@@ -4821,14 +4825,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4844,19 +4848,19 @@
         <v>36</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4906,7 +4910,7 @@
         <v>36</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>34</v>
@@ -4915,22 +4919,22 @@
         <v>35</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>36</v>
@@ -4941,10 +4945,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4952,34 +4956,34 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>36</v>
@@ -5004,13 +5008,13 @@
         <v>36</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>36</v>
@@ -5028,34 +5032,34 @@
         <v>36</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>36</v>
@@ -5063,10 +5067,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5074,13 +5078,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>36</v>
@@ -5089,19 +5093,19 @@
         <v>36</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>36</v>
@@ -5126,29 +5130,29 @@
         <v>36</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>34</v>
@@ -5157,10 +5161,10 @@
         <v>35</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>36</v>
@@ -5169,13 +5173,13 @@
         <v>36</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>36</v>
@@ -5183,26 +5187,26 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>36</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>36</v>
@@ -5211,19 +5215,19 @@
         <v>36</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>36</v>
@@ -5248,13 +5252,13 @@
         <v>36</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>36</v>
@@ -5272,7 +5276,7 @@
         <v>36</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>34</v>
@@ -5281,10 +5285,10 @@
         <v>35</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>36</v>
@@ -5293,13 +5297,13 @@
         <v>36</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>36</v>
@@ -5307,10 +5311,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5321,7 +5325,7 @@
         <v>34</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>36</v>
@@ -5333,13 +5337,13 @@
         <v>36</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -5390,13 +5394,13 @@
         <v>36</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>36</v>
@@ -5414,7 +5418,7 @@
         <v>36</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>36</v>
@@ -5425,14 +5429,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -5451,16 +5455,16 @@
         <v>36</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5498,19 +5502,19 @@
         <v>36</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>34</v>
@@ -5519,10 +5523,10 @@
         <v>35</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>36</v>
@@ -5534,7 +5538,7 @@
         <v>36</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>36</v>
@@ -5545,10 +5549,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5556,34 +5560,34 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>35</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>36</v>
@@ -5632,7 +5636,7 @@
         <v>36</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>34</v>
@@ -5641,10 +5645,10 @@
         <v>35</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>36</v>
@@ -5653,10 +5657,10 @@
         <v>36</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>36</v>
@@ -5667,10 +5671,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5681,7 +5685,7 @@
         <v>34</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>36</v>
@@ -5693,13 +5697,13 @@
         <v>36</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5750,13 +5754,13 @@
         <v>36</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>36</v>
@@ -5774,7 +5778,7 @@
         <v>36</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>36</v>
@@ -5785,14 +5789,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5811,16 +5815,16 @@
         <v>36</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5858,19 +5862,19 @@
         <v>36</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>34</v>
@@ -5879,10 +5883,10 @@
         <v>35</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>36</v>
@@ -5894,7 +5898,7 @@
         <v>36</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>36</v>
@@ -5905,10 +5909,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5916,41 +5920,41 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q31" s="2"/>
       <c r="R31" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="S31" t="s" s="2">
         <v>36</v>
@@ -5992,19 +5996,19 @@
         <v>36</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>36</v>
@@ -6013,10 +6017,10 @@
         <v>36</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>36</v>
@@ -6027,10 +6031,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6041,7 +6045,7 @@
         <v>34</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>36</v>
@@ -6050,19 +6054,19 @@
         <v>36</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6112,19 +6116,19 @@
         <v>36</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>36</v>
@@ -6133,10 +6137,10 @@
         <v>36</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>36</v>
@@ -6147,10 +6151,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6158,41 +6162,41 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>36</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>36</v>
@@ -6234,19 +6238,19 @@
         <v>36</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>36</v>
@@ -6255,10 +6259,10 @@
         <v>36</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>36</v>
@@ -6269,10 +6273,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6283,7 +6287,7 @@
         <v>34</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>36</v>
@@ -6292,22 +6296,22 @@
         <v>36</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>36</v>
@@ -6356,19 +6360,19 @@
         <v>36</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>36</v>
@@ -6377,10 +6381,10 @@
         <v>36</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>36</v>
@@ -6391,10 +6395,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6405,7 +6409,7 @@
         <v>34</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>36</v>
@@ -6414,22 +6418,22 @@
         <v>36</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>36</v>
@@ -6478,19 +6482,19 @@
         <v>36</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>36</v>
@@ -6499,10 +6503,10 @@
         <v>36</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>36</v>
@@ -6513,10 +6517,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6527,7 +6531,7 @@
         <v>34</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>36</v>
@@ -6536,22 +6540,22 @@
         <v>36</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>36</v>
@@ -6600,19 +6604,19 @@
         <v>36</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>36</v>
@@ -6621,10 +6625,10 @@
         <v>36</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>36</v>
@@ -6635,45 +6639,45 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>36</v>
@@ -6698,13 +6702,13 @@
         <v>36</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>36</v>
@@ -6722,45 +6726,45 @@
         <v>36</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6771,7 +6775,7 @@
         <v>34</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>36</v>
@@ -6783,13 +6787,13 @@
         <v>36</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6840,13 +6844,13 @@
         <v>36</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>36</v>
@@ -6864,7 +6868,7 @@
         <v>36</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>36</v>
@@ -6875,14 +6879,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6901,16 +6905,16 @@
         <v>36</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6948,19 +6952,19 @@
         <v>36</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>34</v>
@@ -6969,10 +6973,10 @@
         <v>35</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>36</v>
@@ -6984,7 +6988,7 @@
         <v>36</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>36</v>
@@ -6995,10 +6999,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7018,22 +7022,22 @@
         <v>36</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>36</v>
@@ -7043,7 +7047,7 @@
         <v>36</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>36</v>
@@ -7082,7 +7086,7 @@
         <v>36</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>34</v>
@@ -7091,10 +7095,10 @@
         <v>35</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>36</v>
@@ -7103,10 +7107,10 @@
         <v>36</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>36</v>
@@ -7117,10 +7121,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7131,7 +7135,7 @@
         <v>34</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>36</v>
@@ -7140,22 +7144,22 @@
         <v>36</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>36</v>
@@ -7204,19 +7208,19 @@
         <v>36</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>36</v>
@@ -7225,10 +7229,10 @@
         <v>36</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>36</v>
@@ -7239,10 +7243,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7250,34 +7254,34 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>36</v>
@@ -7326,34 +7330,34 @@
         <v>36</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP42" t="s" s="2">
         <v>36</v>
@@ -7361,10 +7365,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7384,19 +7388,19 @@
         <v>36</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7446,7 +7450,7 @@
         <v>36</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>34</v>
@@ -7455,10 +7459,10 @@
         <v>35</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>36</v>
@@ -7467,13 +7471,13 @@
         <v>36</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>36</v>
@@ -7481,21 +7485,21 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>36</v>
@@ -7504,22 +7508,22 @@
         <v>36</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>36</v>
@@ -7568,34 +7572,34 @@
         <v>36</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>36</v>
@@ -7603,45 +7607,45 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>36</v>
@@ -7690,34 +7694,34 @@
         <v>36</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>36</v>
@@ -7725,10 +7729,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7739,7 +7743,7 @@
         <v>34</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>36</v>
@@ -7748,19 +7752,19 @@
         <v>36</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7810,19 +7814,19 @@
         <v>36</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>36</v>
@@ -7831,13 +7835,13 @@
         <v>36</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>36</v>
@@ -7845,10 +7849,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7868,22 +7872,22 @@
         <v>36</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>36</v>
@@ -7932,7 +7936,7 @@
         <v>36</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>34</v>
@@ -7941,25 +7945,25 @@
         <v>35</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>36</v>
@@ -7967,10 +7971,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7981,31 +7985,31 @@
         <v>34</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>36</v>
@@ -8015,7 +8019,7 @@
         <v>36</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>36</v>
@@ -8054,45 +8058,45 @@
         <v>36</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8103,7 +8107,7 @@
         <v>34</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>36</v>
@@ -8115,13 +8119,13 @@
         <v>36</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -8172,13 +8176,13 @@
         <v>36</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>36</v>
@@ -8196,7 +8200,7 @@
         <v>36</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>36</v>
@@ -8207,14 +8211,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -8233,16 +8237,16 @@
         <v>36</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8280,19 +8284,19 @@
         <v>36</v>
       </c>
       <c r="AB50" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC50" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD50" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>34</v>
@@ -8301,10 +8305,10 @@
         <v>35</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>36</v>
@@ -8316,7 +8320,7 @@
         <v>36</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>36</v>
@@ -8327,10 +8331,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8341,7 +8345,7 @@
         <v>34</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>36</v>
@@ -8350,22 +8354,22 @@
         <v>36</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>36</v>
@@ -8414,19 +8418,19 @@
         <v>36</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>36</v>
@@ -8435,10 +8439,10 @@
         <v>36</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>36</v>
@@ -8449,10 +8453,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8463,94 +8467,94 @@
         <v>34</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>36</v>
       </c>
       <c r="I52" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="P52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="Q52" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="R52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="AH52" t="s" s="2">
         <v>47</v>
       </c>
-      <c r="J52" t="s" s="2">
-        <v>47</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>125</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="P52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="Q52" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="R52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>46</v>
-      </c>
       <c r="AI52" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>36</v>
@@ -8559,10 +8563,10 @@
         <v>36</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>36</v>
@@ -8573,10 +8577,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8584,10 +8588,10 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>36</v>
@@ -8596,22 +8600,22 @@
         <v>36</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>36</v>
@@ -8621,7 +8625,7 @@
         <v>36</v>
       </c>
       <c r="S53" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="T53" t="s" s="2">
         <v>36</v>
@@ -8660,19 +8664,19 @@
         <v>36</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>36</v>
@@ -8681,10 +8685,10 @@
         <v>36</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>36</v>
@@ -8695,10 +8699,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8706,10 +8710,10 @@
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>36</v>
@@ -8718,22 +8722,22 @@
         <v>36</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>36</v>
@@ -8782,19 +8786,19 @@
         <v>36</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>36</v>
@@ -8803,10 +8807,10 @@
         <v>36</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>36</v>
@@ -8817,10 +8821,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8828,10 +8832,10 @@
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>36</v>
@@ -8840,22 +8844,22 @@
         <v>36</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>36</v>
@@ -8904,19 +8908,19 @@
         <v>36</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>36</v>
@@ -8925,10 +8929,10 @@
         <v>36</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>36</v>
@@ -8939,10 +8943,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8953,10 +8957,10 @@
         <v>34</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>36</v>
@@ -8965,19 +8969,19 @@
         <v>36</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>36</v>
@@ -9002,13 +9006,13 @@
         <v>36</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>36</v>
@@ -9026,19 +9030,19 @@
         <v>36</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>36</v>
@@ -9047,10 +9051,10 @@
         <v>36</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>36</v>
@@ -9061,10 +9065,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9075,7 +9079,7 @@
         <v>34</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>36</v>
@@ -9087,13 +9091,13 @@
         <v>36</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9144,13 +9148,13 @@
         <v>36</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>36</v>
@@ -9168,7 +9172,7 @@
         <v>36</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>36</v>
@@ -9179,14 +9183,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9205,16 +9209,16 @@
         <v>36</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9252,19 +9256,19 @@
         <v>36</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>34</v>
@@ -9273,10 +9277,10 @@
         <v>35</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>36</v>
@@ -9288,7 +9292,7 @@
         <v>36</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>36</v>
@@ -9299,10 +9303,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9322,22 +9326,22 @@
         <v>36</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>36</v>
@@ -9386,7 +9390,7 @@
         <v>36</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>34</v>
@@ -9395,10 +9399,10 @@
         <v>35</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>36</v>
@@ -9407,10 +9411,10 @@
         <v>36</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>36</v>
@@ -9421,10 +9425,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9435,7 +9439,7 @@
         <v>34</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>36</v>
@@ -9447,13 +9451,13 @@
         <v>36</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9504,13 +9508,13 @@
         <v>36</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>36</v>
@@ -9528,7 +9532,7 @@
         <v>36</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>36</v>
@@ -9539,14 +9543,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9565,16 +9569,16 @@
         <v>36</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9612,19 +9616,19 @@
         <v>36</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>34</v>
@@ -9633,10 +9637,10 @@
         <v>35</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>36</v>
@@ -9648,7 +9652,7 @@
         <v>36</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>36</v>
@@ -9659,10 +9663,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9670,10 +9674,10 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>36</v>
@@ -9682,22 +9686,22 @@
         <v>36</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>36</v>
@@ -9746,19 +9750,19 @@
         <v>36</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>36</v>
@@ -9767,10 +9771,10 @@
         <v>36</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>36</v>
@@ -9781,10 +9785,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9795,7 +9799,7 @@
         <v>34</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>36</v>
@@ -9804,19 +9808,19 @@
         <v>36</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9866,19 +9870,19 @@
         <v>36</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>36</v>
@@ -9887,10 +9891,10 @@
         <v>36</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>36</v>
@@ -9901,10 +9905,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9912,10 +9916,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>36</v>
@@ -9924,22 +9928,22 @@
         <v>36</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>36</v>
@@ -9988,19 +9992,19 @@
         <v>36</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>36</v>
@@ -10009,10 +10013,10 @@
         <v>36</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>36</v>
@@ -10023,10 +10027,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10037,7 +10041,7 @@
         <v>34</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>36</v>
@@ -10046,22 +10050,22 @@
         <v>36</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>36</v>
@@ -10110,19 +10114,19 @@
         <v>36</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>36</v>
@@ -10131,10 +10135,10 @@
         <v>36</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>36</v>
@@ -10145,10 +10149,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10159,7 +10163,7 @@
         <v>34</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>36</v>
@@ -10168,22 +10172,22 @@
         <v>36</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>36</v>
@@ -10232,19 +10236,19 @@
         <v>36</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>36</v>
@@ -10253,10 +10257,10 @@
         <v>36</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>36</v>
@@ -10267,10 +10271,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10281,7 +10285,7 @@
         <v>34</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>36</v>
@@ -10290,22 +10294,22 @@
         <v>36</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>36</v>
@@ -10354,19 +10358,19 @@
         <v>36</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>36</v>
@@ -10375,10 +10379,10 @@
         <v>36</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>36</v>
@@ -10389,14 +10393,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10415,19 +10419,19 @@
         <v>36</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>36</v>
@@ -10452,13 +10456,13 @@
         <v>36</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>36</v>
@@ -10476,7 +10480,7 @@
         <v>36</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>34</v>
@@ -10485,36 +10489,36 @@
         <v>35</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10537,19 +10541,19 @@
         <v>36</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>36</v>
@@ -10598,7 +10602,7 @@
         <v>36</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>34</v>
@@ -10607,10 +10611,10 @@
         <v>35</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>36</v>
@@ -10619,10 +10623,10 @@
         <v>36</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>36</v>
@@ -10633,10 +10637,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10647,7 +10651,7 @@
         <v>34</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>36</v>
@@ -10659,16 +10663,16 @@
         <v>36</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10694,13 +10698,13 @@
         <v>36</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>36</v>
@@ -10718,45 +10722,45 @@
         <v>36</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10767,7 +10771,7 @@
         <v>34</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>36</v>
@@ -10779,19 +10783,19 @@
         <v>36</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>36</v>
@@ -10816,13 +10820,13 @@
         <v>36</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>36</v>
@@ -10840,19 +10844,19 @@
         <v>36</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>36</v>
@@ -10861,10 +10865,10 @@
         <v>36</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>36</v>
@@ -10875,10 +10879,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10889,7 +10893,7 @@
         <v>34</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>36</v>
@@ -10901,13 +10905,13 @@
         <v>36</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10958,13 +10962,13 @@
         <v>36</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>36</v>
@@ -10982,7 +10986,7 @@
         <v>36</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>36</v>
@@ -10993,14 +10997,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11019,16 +11023,16 @@
         <v>36</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11066,19 +11070,19 @@
         <v>36</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>34</v>
@@ -11087,10 +11091,10 @@
         <v>35</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>36</v>
@@ -11102,7 +11106,7 @@
         <v>36</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>36</v>
@@ -11113,10 +11117,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11136,22 +11140,22 @@
         <v>36</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>36</v>
@@ -11200,7 +11204,7 @@
         <v>36</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>34</v>
@@ -11209,10 +11213,10 @@
         <v>35</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>36</v>
@@ -11221,10 +11225,10 @@
         <v>36</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>36</v>
@@ -11235,10 +11239,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11249,7 +11253,7 @@
         <v>34</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>36</v>
@@ -11261,13 +11265,13 @@
         <v>36</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11318,13 +11322,13 @@
         <v>36</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>36</v>
@@ -11342,7 +11346,7 @@
         <v>36</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>36</v>
@@ -11353,14 +11357,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11379,16 +11383,16 @@
         <v>36</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -11426,19 +11430,19 @@
         <v>36</v>
       </c>
       <c r="AB76" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC76" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD76" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE76" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>34</v>
@@ -11447,10 +11451,10 @@
         <v>35</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>36</v>
@@ -11462,7 +11466,7 @@
         <v>36</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>36</v>
@@ -11473,10 +11477,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11484,10 +11488,10 @@
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>36</v>
@@ -11496,22 +11500,22 @@
         <v>36</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>36</v>
@@ -11560,19 +11564,19 @@
         <v>36</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>36</v>
@@ -11581,10 +11585,10 @@
         <v>36</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>36</v>
@@ -11595,10 +11599,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11609,7 +11613,7 @@
         <v>34</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>36</v>
@@ -11618,19 +11622,19 @@
         <v>36</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11680,19 +11684,19 @@
         <v>36</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>36</v>
@@ -11701,10 +11705,10 @@
         <v>36</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>36</v>
@@ -11715,10 +11719,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11726,10 +11730,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>36</v>
@@ -11738,22 +11742,22 @@
         <v>36</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>36</v>
@@ -11802,19 +11806,19 @@
         <v>36</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>36</v>
@@ -11823,10 +11827,10 @@
         <v>36</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>36</v>
@@ -11837,10 +11841,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11851,7 +11855,7 @@
         <v>34</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>36</v>
@@ -11860,22 +11864,22 @@
         <v>36</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>36</v>
@@ -11924,19 +11928,19 @@
         <v>36</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>36</v>
@@ -11945,10 +11949,10 @@
         <v>36</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>36</v>
@@ -11959,10 +11963,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11973,7 +11977,7 @@
         <v>34</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>36</v>
@@ -11982,22 +11986,22 @@
         <v>36</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>36</v>
@@ -12046,19 +12050,19 @@
         <v>36</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>36</v>
@@ -12067,10 +12071,10 @@
         <v>36</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>36</v>
@@ -12081,10 +12085,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12095,7 +12099,7 @@
         <v>34</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>36</v>
@@ -12104,22 +12108,22 @@
         <v>36</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>36</v>
@@ -12168,19 +12172,19 @@
         <v>36</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK82" t="s" s="2">
         <v>36</v>
@@ -12189,10 +12193,10 @@
         <v>36</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>36</v>
@@ -12203,10 +12207,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12217,7 +12221,7 @@
         <v>34</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>36</v>
@@ -12229,16 +12233,16 @@
         <v>36</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -12288,45 +12292,45 @@
         <v>36</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12337,7 +12341,7 @@
         <v>34</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>36</v>
@@ -12349,16 +12353,16 @@
         <v>36</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12408,45 +12412,45 @@
         <v>36</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12469,19 +12473,19 @@
         <v>36</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>36</v>
@@ -12530,7 +12534,7 @@
         <v>36</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>34</v>
@@ -12539,10 +12543,10 @@
         <v>35</v>
       </c>
       <c r="AI85" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>36</v>
@@ -12551,10 +12555,10 @@
         <v>36</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>36</v>
@@ -12565,10 +12569,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12579,7 +12583,7 @@
         <v>34</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>36</v>
@@ -12591,13 +12595,13 @@
         <v>36</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12648,13 +12652,13 @@
         <v>36</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>36</v>
@@ -12672,7 +12676,7 @@
         <v>36</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>36</v>
@@ -12683,14 +12687,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -12709,16 +12713,16 @@
         <v>36</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12756,19 +12760,19 @@
         <v>36</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>34</v>
@@ -12777,10 +12781,10 @@
         <v>35</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>36</v>
@@ -12792,7 +12796,7 @@
         <v>36</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>36</v>
@@ -12803,14 +12807,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12823,25 +12827,25 @@
         <v>36</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>36</v>
@@ -12890,7 +12894,7 @@
         <v>36</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>34</v>
@@ -12899,10 +12903,10 @@
         <v>35</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>36</v>
@@ -12914,7 +12918,7 @@
         <v>36</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>36</v>
@@ -12925,10 +12929,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12939,7 +12943,7 @@
         <v>34</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>36</v>
@@ -12951,16 +12955,16 @@
         <v>36</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13010,19 +13014,19 @@
         <v>36</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>36</v>
@@ -13031,10 +13035,10 @@
         <v>36</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>36</v>
@@ -13045,10 +13049,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13059,7 +13063,7 @@
         <v>34</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>36</v>
@@ -13071,16 +13075,16 @@
         <v>36</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13130,19 +13134,19 @@
         <v>36</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>36</v>
@@ -13151,10 +13155,10 @@
         <v>36</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>36</v>
@@ -13165,10 +13169,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13179,7 +13183,7 @@
         <v>34</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>36</v>
@@ -13191,19 +13195,19 @@
         <v>36</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>36</v>
@@ -13228,13 +13232,13 @@
         <v>36</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>36</v>
@@ -13252,31 +13256,31 @@
         <v>36</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>36</v>
@@ -13287,10 +13291,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13313,19 +13317,19 @@
         <v>36</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>36</v>
@@ -13350,13 +13354,13 @@
         <v>36</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>36</v>
@@ -13374,7 +13378,7 @@
         <v>36</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>34</v>
@@ -13383,22 +13387,22 @@
         <v>35</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ92" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK92" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>36</v>
@@ -13409,10 +13413,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13423,7 +13427,7 @@
         <v>34</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>36</v>
@@ -13435,19 +13439,19 @@
         <v>36</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>36</v>
@@ -13496,19 +13500,19 @@
         <v>36</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>36</v>
@@ -13517,10 +13521,10 @@
         <v>36</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>36</v>
@@ -13531,10 +13535,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13545,7 +13549,7 @@
         <v>34</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>36</v>
@@ -13557,16 +13561,16 @@
         <v>36</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13616,19 +13620,19 @@
         <v>36</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>36</v>
@@ -13637,10 +13641,10 @@
         <v>36</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>36</v>
@@ -13651,10 +13655,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13674,19 +13678,19 @@
         <v>36</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13736,7 +13740,7 @@
         <v>36</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>34</v>
@@ -13745,10 +13749,10 @@
         <v>35</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>36</v>
@@ -13757,10 +13761,10 @@
         <v>36</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>36</v>
@@ -13771,10 +13775,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13794,19 +13798,19 @@
         <v>36</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13856,7 +13860,7 @@
         <v>36</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>34</v>
@@ -13865,10 +13869,10 @@
         <v>35</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>36</v>
@@ -13877,10 +13881,10 @@
         <v>36</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>36</v>
@@ -13891,10 +13895,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13908,28 +13912,28 @@
         <v>35</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>36</v>
@@ -13978,7 +13982,7 @@
         <v>36</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>34</v>
@@ -13987,10 +13991,10 @@
         <v>35</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>36</v>
@@ -13999,10 +14003,10 @@
         <v>36</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>36</v>
@@ -14013,10 +14017,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14027,7 +14031,7 @@
         <v>34</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>36</v>
@@ -14039,13 +14043,13 @@
         <v>36</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -14096,13 +14100,13 @@
         <v>36</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>36</v>
@@ -14120,7 +14124,7 @@
         <v>36</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>36</v>
@@ -14131,14 +14135,14 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -14157,16 +14161,16 @@
         <v>36</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -14204,19 +14208,19 @@
         <v>36</v>
       </c>
       <c r="AB99" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AC99" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AD99" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AE99" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>34</v>
@@ -14225,10 +14229,10 @@
         <v>35</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>36</v>
@@ -14240,7 +14244,7 @@
         <v>36</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>36</v>
@@ -14251,14 +14255,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14271,25 +14275,25 @@
         <v>36</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>36</v>
@@ -14338,7 +14342,7 @@
         <v>36</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>34</v>
@@ -14347,10 +14351,10 @@
         <v>35</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>36</v>
@@ -14362,7 +14366,7 @@
         <v>36</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>36</v>
@@ -14373,10 +14377,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14384,34 +14388,34 @@
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I101" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>36</v>
@@ -14436,13 +14440,13 @@
         <v>36</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>36</v>
@@ -14460,34 +14464,34 @@
         <v>36</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>36</v>
@@ -14495,10 +14499,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14509,31 +14513,31 @@
         <v>34</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H102" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I102" t="s" s="2">
         <v>36</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>36</v>
@@ -14558,13 +14562,13 @@
         <v>36</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>36</v>
@@ -14582,45 +14586,45 @@
         <v>36</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14631,10 +14635,10 @@
         <v>34</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H103" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I103" t="s" s="2">
         <v>36</v>
@@ -14643,19 +14647,19 @@
         <v>36</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>36</v>
@@ -14680,13 +14684,13 @@
         <v>36</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>36</v>
@@ -14704,19 +14708,19 @@
         <v>36</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>34</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK103" t="s" s="2">
         <v>36</v>
@@ -14725,10 +14729,10 @@
         <v>36</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>36</v>
@@ -14739,14 +14743,14 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
@@ -14765,19 +14769,19 @@
         <v>36</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>36</v>
@@ -14802,13 +14806,13 @@
         <v>36</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>36</v>
@@ -14826,7 +14830,7 @@
         <v>36</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>34</v>
@@ -14835,36 +14839,36 @@
         <v>35</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AJ104" t="s" s="2">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AK104" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>36</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14890,16 +14894,16 @@
         <v>37</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>36</v>
@@ -14948,7 +14952,7 @@
         <v>36</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>34</v>
@@ -14969,10 +14973,10 @@
         <v>36</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>36</v>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:09:26+00:00</t>
+    <t>2023-09-19T16:18:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-19T16:18:04+00:00</t>
+    <t>2023-09-20T15:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-09-20T15:08:45+00:00</t>
+    <t>2023-09-27T13:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-17T15:45:14+00:00</t>
+    <t>2023-11-23T10:14:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4108" uniqueCount="661">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4108" uniqueCount="662">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-23T10:14:09+00:00</t>
+    <t>2023-11-28T12:14:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
+  </si>
+  <si>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -3442,10 +3445,10 @@
         <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -3495,7 +3498,7 @@
         <v>80</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -3530,10 +3533,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -3556,16 +3559,16 @@
         <v>92</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -3615,7 +3618,7 @@
         <v>80</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3650,10 +3653,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -3676,16 +3679,16 @@
         <v>92</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -3711,13 +3714,13 @@
         <v>80</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>80</v>
@@ -3735,7 +3738,7 @@
         <v>80</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3756,10 +3759,10 @@
         <v>80</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN11" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO11" t="s" s="2">
         <v>80</v>
@@ -3770,10 +3773,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3796,16 +3799,16 @@
         <v>92</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3831,13 +3834,13 @@
         <v>80</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>80</v>
@@ -3855,7 +3858,7 @@
         <v>80</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3876,10 +3879,10 @@
         <v>80</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>80</v>
@@ -3890,10 +3893,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3919,13 +3922,13 @@
         <v>135</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3975,7 +3978,7 @@
         <v>80</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -4010,10 +4013,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4036,16 +4039,16 @@
         <v>80</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4071,13 +4074,13 @@
         <v>80</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>80</v>
@@ -4095,7 +4098,7 @@
         <v>80</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -4130,14 +4133,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -4156,16 +4159,16 @@
         <v>80</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4215,7 +4218,7 @@
         <v>80</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4239,7 +4242,7 @@
         <v>80</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>80</v>
@@ -4250,14 +4253,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4276,16 +4279,16 @@
         <v>80</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4335,7 +4338,7 @@
         <v>80</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -4370,10 +4373,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4402,7 +4405,7 @@
         <v>115</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
         <v>117</v>
@@ -4455,7 +4458,7 @@
         <v>120</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4490,13 +4493,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>80</v>
@@ -4518,13 +4521,13 @@
         <v>80</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4575,7 +4578,7 @@
         <v>80</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4610,13 +4613,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>80</v>
@@ -4638,13 +4641,13 @@
         <v>80</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4695,7 +4698,7 @@
         <v>80</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4730,10 +4733,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4759,16 +4762,16 @@
         <v>114</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>80</v>
@@ -4817,7 +4820,7 @@
         <v>120</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4852,10 +4855,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4878,17 +4881,17 @@
         <v>92</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>80</v>
@@ -4937,7 +4940,7 @@
         <v>80</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4952,19 +4955,19 @@
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>80</v>
@@ -4972,14 +4975,14 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4998,19 +5001,19 @@
         <v>92</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5059,7 +5062,7 @@
         <v>80</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -5071,19 +5074,19 @@
         <v>103</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>80</v>
@@ -5094,14 +5097,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5120,16 +5123,16 @@
         <v>92</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5179,7 +5182,7 @@
         <v>80</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5191,19 +5194,19 @@
         <v>103</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>80</v>
@@ -5214,10 +5217,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5240,19 +5243,19 @@
         <v>92</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>80</v>
@@ -5277,13 +5280,13 @@
         <v>80</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>80</v>
@@ -5301,7 +5304,7 @@
         <v>80</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>91</v>
@@ -5316,19 +5319,19 @@
         <v>104</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>80</v>
@@ -5336,10 +5339,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5362,19 +5365,19 @@
         <v>80</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>80</v>
@@ -5399,19 +5402,19 @@
         <v>80</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AB25" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AC25" s="2"/>
       <c r="AD25" t="s" s="2">
@@ -5421,7 +5424,7 @@
         <v>120</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5442,13 +5445,13 @@
         <v>80</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>80</v>
@@ -5456,13 +5459,13 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D26" t="s" s="2">
         <v>80</v>
@@ -5484,19 +5487,19 @@
         <v>80</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>80</v>
@@ -5521,13 +5524,13 @@
         <v>80</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>80</v>
@@ -5545,7 +5548,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5566,13 +5569,13 @@
         <v>80</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>80</v>
@@ -5580,10 +5583,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5698,10 +5701,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5818,10 +5821,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5844,19 +5847,19 @@
         <v>92</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>80</v>
@@ -5905,7 +5908,7 @@
         <v>80</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5926,10 +5929,10 @@
         <v>80</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>80</v>
@@ -5940,10 +5943,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6058,10 +6061,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6178,10 +6181,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6207,23 +6210,23 @@
         <v>135</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>80</v>
@@ -6265,7 +6268,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6286,10 +6289,10 @@
         <v>80</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -6300,10 +6303,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6329,13 +6332,13 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6385,7 +6388,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6406,10 +6409,10 @@
         <v>80</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -6420,10 +6423,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6446,26 +6449,26 @@
         <v>92</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>80</v>
@@ -6507,7 +6510,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6528,10 +6531,10 @@
         <v>80</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -6542,10 +6545,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6571,16 +6574,16 @@
         <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -6629,7 +6632,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6650,10 +6653,10 @@
         <v>80</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -6664,10 +6667,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6690,19 +6693,19 @@
         <v>92</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>80</v>
@@ -6751,7 +6754,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6772,10 +6775,10 @@
         <v>80</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>80</v>
@@ -6786,10 +6789,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6815,16 +6818,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -6873,7 +6876,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6894,10 +6897,10 @@
         <v>80</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>80</v>
@@ -6908,14 +6911,14 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -6934,19 +6937,19 @@
         <v>92</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>80</v>
@@ -6971,13 +6974,13 @@
         <v>80</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>80</v>
@@ -6995,7 +6998,7 @@
         <v>80</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>91</v>
@@ -7010,30 +7013,30 @@
         <v>104</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7148,10 +7151,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7268,10 +7271,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7294,19 +7297,19 @@
         <v>92</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -7316,7 +7319,7 @@
         <v>80</v>
       </c>
       <c r="S41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="T41" t="s" s="2">
         <v>80</v>
@@ -7355,7 +7358,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7376,10 +7379,10 @@
         <v>80</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -7390,10 +7393,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7419,16 +7422,16 @@
         <v>107</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -7477,7 +7480,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7498,10 +7501,10 @@
         <v>80</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -7512,10 +7515,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7538,19 +7541,19 @@
         <v>92</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>80</v>
@@ -7599,7 +7602,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7611,22 +7614,22 @@
         <v>103</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>80</v>
@@ -7634,10 +7637,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7660,16 +7663,16 @@
         <v>92</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7719,7 +7722,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7731,7 +7734,7 @@
         <v>103</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>80</v>
@@ -7740,13 +7743,13 @@
         <v>80</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>80</v>
@@ -7754,14 +7757,14 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -7780,19 +7783,19 @@
         <v>92</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>80</v>
@@ -7841,7 +7844,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7853,22 +7856,22 @@
         <v>103</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>80</v>
@@ -7876,14 +7879,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7902,19 +7905,19 @@
         <v>92</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>80</v>
@@ -7963,7 +7966,7 @@
         <v>80</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7972,25 +7975,25 @@
         <v>91</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>80</v>
@@ -7998,10 +8001,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8027,13 +8030,13 @@
         <v>129</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8083,7 +8086,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -8104,13 +8107,13 @@
         <v>80</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>80</v>
@@ -8118,10 +8121,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8144,19 +8147,19 @@
         <v>92</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>80</v>
@@ -8205,7 +8208,7 @@
         <v>80</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8217,22 +8220,22 @@
         <v>103</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AP48" t="s" s="2">
         <v>80</v>
@@ -8240,10 +8243,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8266,19 +8269,19 @@
         <v>92</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>80</v>
@@ -8288,7 +8291,7 @@
         <v>80</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="T49" t="s" s="2">
         <v>80</v>
@@ -8327,7 +8330,7 @@
         <v>80</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8336,7 +8339,7 @@
         <v>91</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>104</v>
@@ -8345,27 +8348,27 @@
         <v>80</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8480,10 +8483,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8600,10 +8603,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8626,19 +8629,19 @@
         <v>92</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
@@ -8687,7 +8690,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8708,10 +8711,10 @@
         <v>80</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -8722,10 +8725,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8748,25 +8751,25 @@
         <v>92</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q53" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="R53" t="s" s="2">
         <v>80</v>
@@ -8787,13 +8790,13 @@
         <v>80</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>80</v>
@@ -8811,7 +8814,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8832,10 +8835,10 @@
         <v>80</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -8846,10 +8849,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8875,16 +8878,16 @@
         <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>80</v>
@@ -8894,7 +8897,7 @@
         <v>80</v>
       </c>
       <c r="S54" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="T54" t="s" s="2">
         <v>80</v>
@@ -8933,7 +8936,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8954,10 +8957,10 @@
         <v>80</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -8968,10 +8971,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8997,16 +9000,16 @@
         <v>135</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>80</v>
@@ -9055,7 +9058,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -9064,7 +9067,7 @@
         <v>91</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>104</v>
@@ -9076,10 +9079,10 @@
         <v>80</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -9090,10 +9093,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9116,19 +9119,19 @@
         <v>92</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>80</v>
@@ -9177,7 +9180,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9198,10 +9201,10 @@
         <v>80</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
@@ -9212,10 +9215,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9238,19 +9241,19 @@
         <v>80</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>80</v>
@@ -9275,13 +9278,13 @@
         <v>80</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -9299,7 +9302,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9308,7 +9311,7 @@
         <v>91</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>104</v>
@@ -9323,7 +9326,7 @@
         <v>105</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
@@ -9334,10 +9337,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9452,10 +9455,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9572,10 +9575,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9598,19 +9601,19 @@
         <v>92</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>80</v>
@@ -9659,7 +9662,7 @@
         <v>80</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9680,10 +9683,10 @@
         <v>80</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>80</v>
@@ -9694,10 +9697,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9812,10 +9815,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9932,10 +9935,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9961,16 +9964,16 @@
         <v>135</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>80</v>
@@ -10019,7 +10022,7 @@
         <v>80</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -10040,10 +10043,10 @@
         <v>80</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>80</v>
@@ -10054,10 +10057,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10083,13 +10086,13 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -10139,7 +10142,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10160,10 +10163,10 @@
         <v>80</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -10174,10 +10177,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10200,19 +10203,19 @@
         <v>92</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>80</v>
@@ -10261,7 +10264,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10282,10 +10285,10 @@
         <v>80</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
@@ -10296,10 +10299,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10325,16 +10328,16 @@
         <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -10383,7 +10386,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10404,10 +10407,10 @@
         <v>80</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -10418,10 +10421,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10444,19 +10447,19 @@
         <v>92</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -10505,7 +10508,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10526,10 +10529,10 @@
         <v>80</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
@@ -10540,10 +10543,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10569,16 +10572,16 @@
         <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -10627,7 +10630,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10648,10 +10651,10 @@
         <v>80</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
@@ -10662,14 +10665,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10688,19 +10691,19 @@
         <v>80</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -10725,13 +10728,13 @@
         <v>80</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>80</v>
@@ -10749,7 +10752,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10767,27 +10770,27 @@
         <v>80</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10810,19 +10813,19 @@
         <v>80</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>80</v>
@@ -10871,7 +10874,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10892,10 +10895,10 @@
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>80</v>
@@ -10906,10 +10909,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10932,16 +10935,16 @@
         <v>80</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10967,13 +10970,13 @@
         <v>80</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>80</v>
@@ -10991,7 +10994,7 @@
         <v>80</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -11009,27 +11012,27 @@
         <v>80</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11052,19 +11055,19 @@
         <v>80</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>80</v>
@@ -11089,13 +11092,13 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>80</v>
@@ -11113,7 +11116,7 @@
         <v>80</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -11134,10 +11137,10 @@
         <v>80</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>80</v>
@@ -11148,10 +11151,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11266,10 +11269,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11386,10 +11389,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11412,19 +11415,19 @@
         <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11473,7 +11476,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11494,10 +11497,10 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11508,10 +11511,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11626,10 +11629,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11746,10 +11749,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11775,16 +11778,16 @@
         <v>135</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11833,7 +11836,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11854,10 +11857,10 @@
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11868,10 +11871,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11897,13 +11900,13 @@
         <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11953,7 +11956,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11974,10 +11977,10 @@
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -11988,10 +11991,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12014,19 +12017,19 @@
         <v>92</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -12075,7 +12078,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12096,10 +12099,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12110,10 +12113,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12139,16 +12142,16 @@
         <v>107</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -12197,7 +12200,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12218,10 +12221,10 @@
         <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12232,10 +12235,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12258,19 +12261,19 @@
         <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -12319,7 +12322,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12340,10 +12343,10 @@
         <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12354,10 +12357,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12383,16 +12386,16 @@
         <v>107</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -12441,7 +12444,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12462,10 +12465,10 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -12476,10 +12479,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12502,16 +12505,16 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12561,7 +12564,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12573,33 +12576,33 @@
         <v>103</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12622,16 +12625,16 @@
         <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12681,7 +12684,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12693,33 +12696,33 @@
         <v>103</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12742,19 +12745,19 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
@@ -12803,7 +12806,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12815,7 +12818,7 @@
         <v>103</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>80</v>
@@ -12824,10 +12827,10 @@
         <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -12838,10 +12841,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12956,10 +12959,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13076,14 +13079,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13105,16 +13108,16 @@
         <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
@@ -13163,7 +13166,7 @@
         <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13198,10 +13201,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13224,16 +13227,16 @@
         <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13283,7 +13286,7 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13292,10 +13295,10 @@
         <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
@@ -13304,10 +13307,10 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13318,10 +13321,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13344,16 +13347,16 @@
         <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -13403,7 +13406,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13412,10 +13415,10 @@
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
@@ -13424,10 +13427,10 @@
         <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>80</v>
@@ -13438,10 +13441,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13464,19 +13467,19 @@
         <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13501,13 +13504,13 @@
         <v>80</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
@@ -13525,7 +13528,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13543,13 +13546,13 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -13560,10 +13563,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13586,19 +13589,19 @@
         <v>80</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13623,13 +13626,13 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13647,7 +13650,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13665,13 +13668,13 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13682,10 +13685,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13708,19 +13711,19 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13769,7 +13772,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13781,7 +13784,7 @@
         <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
@@ -13790,10 +13793,10 @@
         <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -13804,10 +13807,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13833,13 +13836,13 @@
         <v>107</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13889,7 +13892,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13910,10 +13913,10 @@
         <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
@@ -13924,10 +13927,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13950,16 +13953,16 @@
         <v>92</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14009,7 +14012,7 @@
         <v>80</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -14021,7 +14024,7 @@
         <v>103</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>80</v>
@@ -14030,10 +14033,10 @@
         <v>80</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>80</v>
@@ -14044,10 +14047,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14070,16 +14073,16 @@
         <v>92</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -14129,7 +14132,7 @@
         <v>80</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -14141,7 +14144,7 @@
         <v>103</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>80</v>
@@ -14150,10 +14153,10 @@
         <v>80</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>80</v>
@@ -14164,10 +14167,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14190,19 +14193,19 @@
         <v>92</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
@@ -14251,7 +14254,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14263,7 +14266,7 @@
         <v>103</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>80</v>
@@ -14272,10 +14275,10 @@
         <v>80</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -14286,10 +14289,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14404,10 +14407,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14524,14 +14527,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14553,16 +14556,16 @@
         <v>114</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N101" t="s" s="2">
         <v>117</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -14611,7 +14614,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14646,10 +14649,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14672,19 +14675,19 @@
         <v>92</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>80</v>
@@ -14709,13 +14712,13 @@
         <v>80</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>80</v>
@@ -14733,7 +14736,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>91</v>
@@ -14751,16 +14754,16 @@
         <v>80</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP102" t="s" s="2">
         <v>80</v>
@@ -14768,10 +14771,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14794,19 +14797,19 @@
         <v>92</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -14831,13 +14834,13 @@
         <v>80</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>80</v>
@@ -14855,7 +14858,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14864,7 +14867,7 @@
         <v>91</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>104</v>
@@ -14873,27 +14876,27 @@
         <v>80</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14916,19 +14919,19 @@
         <v>80</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -14953,13 +14956,13 @@
         <v>80</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>80</v>
@@ -14977,7 +14980,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14986,7 +14989,7 @@
         <v>91</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>104</v>
@@ -15001,7 +15004,7 @@
         <v>105</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -15012,14 +15015,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -15038,19 +15041,19 @@
         <v>80</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -15075,13 +15078,13 @@
         <v>80</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>80</v>
@@ -15099,7 +15102,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -15117,27 +15120,27 @@
         <v>80</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15163,16 +15166,16 @@
         <v>81</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -15221,7 +15224,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15242,10 +15245,10 @@
         <v>80</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4108" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3685" uniqueCount="651">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:14:54+00:00</t>
+    <t>2023-11-28T12:15:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1660,39 +1660,6 @@
   </si>
   <si>
     <t>methodCode</t>
-  </si>
-  <si>
-    <t>Observation.method.id</t>
-  </si>
-  <si>
-    <t>Observation.method.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.method.text</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -2401,7 +2368,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP106"/>
+  <dimension ref="A1:AP95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
@@ -11046,7 +11013,7 @@
         <v>91</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>80</v>
@@ -11092,11 +11059,9 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>525</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
         <v>525</v>
       </c>
@@ -11177,15 +11142,17 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>107</v>
+        <v>529</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>108</v>
+        <v>530</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -11234,7 +11201,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>110</v>
+        <v>528</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11243,47 +11210,47 @@
         <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>80</v>
+        <v>533</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>80</v>
+        <v>534</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>111</v>
+        <v>535</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>80</v>
+        <v>536</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
@@ -11295,16 +11262,16 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>114</v>
+        <v>538</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>115</v>
+        <v>539</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>116</v>
+        <v>540</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>117</v>
+        <v>541</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11342,57 +11309,57 @@
         <v>80</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>121</v>
+        <v>537</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>80</v>
+        <v>542</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>80</v>
+        <v>543</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>105</v>
+        <v>544</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>80</v>
+        <v>545</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11412,22 +11379,22 @@
         <v>80</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>147</v>
+        <v>547</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>274</v>
+        <v>548</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>275</v>
+        <v>549</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>276</v>
+        <v>550</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>277</v>
+        <v>551</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11476,7 +11443,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>278</v>
+        <v>546</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11488,7 +11455,7 @@
         <v>103</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>104</v>
+        <v>552</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
@@ -11497,10 +11464,10 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>279</v>
+        <v>553</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>280</v>
+        <v>554</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11511,10 +11478,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11629,10 +11596,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11749,45 +11716,45 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>80</v>
+        <v>558</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J78" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>287</v>
+        <v>559</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>288</v>
+        <v>560</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>289</v>
+        <v>117</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11836,19 +11803,19 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>292</v>
+        <v>561</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>80</v>
@@ -11857,10 +11824,10 @@
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>294</v>
+        <v>105</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11871,10 +11838,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>534</v>
+        <v>562</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>534</v>
+        <v>562</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11894,19 +11861,19 @@
         <v>80</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>107</v>
+        <v>563</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>297</v>
+        <v>564</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>298</v>
+        <v>565</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>299</v>
+        <v>566</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11956,7 +11923,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>300</v>
+        <v>562</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11965,10 +11932,10 @@
         <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>103</v>
+        <v>567</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>104</v>
+        <v>568</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11977,10 +11944,10 @@
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>301</v>
+        <v>569</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>302</v>
+        <v>570</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -11991,10 +11958,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>535</v>
+        <v>571</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>535</v>
+        <v>571</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12002,7 +11969,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>91</v>
@@ -12014,23 +11981,21 @@
         <v>80</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>171</v>
+        <v>563</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>305</v>
+        <v>572</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>306</v>
+        <v>573</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
       </c>
@@ -12078,7 +12043,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>310</v>
+        <v>571</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12087,10 +12052,10 @@
         <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>103</v>
+        <v>567</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>104</v>
+        <v>568</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>80</v>
@@ -12099,10 +12064,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>311</v>
+        <v>569</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>312</v>
+        <v>574</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12113,10 +12078,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>536</v>
+        <v>575</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>536</v>
+        <v>575</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12136,22 +12101,22 @@
         <v>80</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>315</v>
+        <v>576</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>316</v>
+        <v>577</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>307</v>
+        <v>578</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>317</v>
+        <v>579</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -12176,13 +12141,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>80</v>
+        <v>581</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -12200,7 +12165,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>318</v>
+        <v>575</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12218,13 +12183,13 @@
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>80</v>
+        <v>582</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>319</v>
+        <v>583</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12235,10 +12200,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12249,7 +12214,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -12258,22 +12223,22 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>323</v>
+        <v>255</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>324</v>
+        <v>585</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>325</v>
+        <v>586</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>326</v>
+        <v>587</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>327</v>
+        <v>588</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -12298,13 +12263,13 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>80</v>
+        <v>589</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>80</v>
+        <v>590</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>80</v>
@@ -12322,13 +12287,13 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>328</v>
+        <v>584</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>103</v>
@@ -12340,13 +12305,13 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>80</v>
+        <v>582</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>329</v>
+        <v>583</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12357,10 +12322,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>538</v>
+        <v>591</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>538</v>
+        <v>591</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12380,22 +12345,22 @@
         <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>107</v>
+        <v>592</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>333</v>
+        <v>593</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>334</v>
+        <v>594</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>335</v>
+        <v>595</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>336</v>
+        <v>596</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -12444,7 +12409,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>337</v>
+        <v>591</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12456,7 +12421,7 @@
         <v>103</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>104</v>
+        <v>597</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
@@ -12465,10 +12430,10 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>338</v>
+        <v>598</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>339</v>
+        <v>599</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -12479,10 +12444,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>539</v>
+        <v>600</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>539</v>
+        <v>600</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12505,16 +12470,16 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>540</v>
+        <v>107</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>541</v>
+        <v>601</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>542</v>
+        <v>602</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>543</v>
+        <v>307</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12564,7 +12529,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>539</v>
+        <v>600</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12576,33 +12541,33 @@
         <v>103</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>228</v>
+        <v>104</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>544</v>
+        <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>546</v>
+        <v>603</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>547</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12613,7 +12578,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12622,19 +12587,19 @@
         <v>80</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>549</v>
+        <v>605</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>550</v>
+        <v>606</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>551</v>
+        <v>607</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>552</v>
+        <v>608</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12684,13 +12649,13 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>103</v>
@@ -12702,27 +12667,27 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>553</v>
+        <v>80</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>554</v>
+        <v>609</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>555</v>
+        <v>610</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>556</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>557</v>
+        <v>611</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>557</v>
+        <v>611</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12742,23 +12707,21 @@
         <v>80</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>558</v>
+        <v>612</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>559</v>
+        <v>613</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>560</v>
+        <v>614</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>80</v>
       </c>
@@ -12806,7 +12769,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>557</v>
+        <v>611</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12818,7 +12781,7 @@
         <v>103</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>563</v>
+        <v>228</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>80</v>
@@ -12827,10 +12790,10 @@
         <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>564</v>
+        <v>609</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>565</v>
+        <v>616</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -12841,10 +12804,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>566</v>
+        <v>617</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>566</v>
+        <v>617</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12855,28 +12818,32 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>107</v>
+        <v>547</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>108</v>
+        <v>618</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>618</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>620</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
       </c>
@@ -12924,19 +12891,19 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>110</v>
+        <v>617</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>80</v>
+        <v>621</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>80</v>
@@ -12945,10 +12912,10 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>80</v>
+        <v>622</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>111</v>
+        <v>623</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -12959,21 +12926,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>567</v>
+        <v>624</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>567</v>
+        <v>624</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>80</v>
@@ -12985,17 +12952,15 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -13032,31 +12997,31 @@
         <v>80</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
@@ -13068,7 +13033,7 @@
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13079,14 +13044,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>568</v>
+        <v>625</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>568</v>
+        <v>625</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>569</v>
+        <v>113</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13099,26 +13064,24 @@
         <v>80</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>570</v>
+        <v>115</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>571</v>
+        <v>116</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O89" t="s" s="2">
-        <v>210</v>
-      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>80</v>
       </c>
@@ -13154,19 +13117,19 @@
         <v>80</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>572</v>
+        <v>121</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13201,44 +13164,46 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>573</v>
+        <v>626</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>573</v>
+        <v>626</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>80</v>
+        <v>558</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>574</v>
+        <v>114</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
       </c>
@@ -13286,19 +13251,19 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>578</v>
+        <v>103</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>579</v>
+        <v>122</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
@@ -13307,10 +13272,10 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>581</v>
+        <v>105</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13321,10 +13286,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>582</v>
+        <v>627</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>582</v>
+        <v>627</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13332,33 +13297,35 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>574</v>
+        <v>255</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>583</v>
+        <v>628</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>584</v>
+        <v>629</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>630</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13382,13 +13349,13 @@
         <v>80</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>80</v>
@@ -13406,34 +13373,34 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>582</v>
+        <v>627</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>578</v>
+        <v>103</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>579</v>
+        <v>104</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>80</v>
+        <v>632</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>580</v>
+        <v>350</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>585</v>
+        <v>351</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>80</v>
@@ -13441,10 +13408,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13458,28 +13425,28 @@
         <v>91</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>255</v>
+        <v>634</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>587</v>
+        <v>635</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>588</v>
+        <v>636</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>589</v>
+        <v>637</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>590</v>
+        <v>419</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13504,13 +13471,13 @@
         <v>80</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>175</v>
+        <v>246</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>591</v>
+        <v>638</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>592</v>
+        <v>639</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
@@ -13528,7 +13495,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13537,7 +13504,7 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>103</v>
+        <v>640</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>104</v>
@@ -13546,27 +13513,27 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>593</v>
+        <v>641</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>594</v>
+        <v>423</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>500</v>
+        <v>424</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>80</v>
+        <v>425</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>595</v>
+        <v>642</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>595</v>
+        <v>642</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13577,10 +13544,10 @@
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>80</v>
@@ -13592,16 +13559,16 @@
         <v>255</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>596</v>
+        <v>643</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>597</v>
+        <v>644</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>598</v>
+        <v>645</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>599</v>
+        <v>474</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13626,13 +13593,13 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>600</v>
+        <v>475</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>601</v>
+        <v>476</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13650,16 +13617,16 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>595</v>
+        <v>642</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>103</v>
+        <v>646</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>104</v>
@@ -13668,13 +13635,13 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>593</v>
+        <v>80</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>594</v>
+        <v>105</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13685,21 +13652,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>602</v>
+        <v>647</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>602</v>
+        <v>647</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>80</v>
+        <v>491</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>80</v>
@@ -13711,19 +13678,19 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>603</v>
+        <v>255</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>604</v>
+        <v>492</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>605</v>
+        <v>493</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>606</v>
+        <v>494</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>607</v>
+        <v>495</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13748,13 +13715,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>80</v>
+        <v>496</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>80</v>
+        <v>497</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13772,45 +13739,45 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>602</v>
+        <v>647</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>608</v>
+        <v>104</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>80</v>
+        <v>498</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>609</v>
+        <v>499</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>610</v>
+        <v>500</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>80</v>
+        <v>501</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13821,7 +13788,7 @@
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>80</v>
@@ -13833,18 +13800,20 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>612</v>
+        <v>649</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>613</v>
+        <v>650</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
       </c>
@@ -13892,19 +13861,19 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
@@ -13913,1352 +13882,20 @@
         <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>580</v>
+        <v>553</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>614</v>
+        <v>554</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP106" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP106">
+  <autoFilter ref="A1:AP95">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15268,7 +13905,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI105">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$95</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$106</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3685" uniqueCount="651">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4108" uniqueCount="662">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:15:35+00:00</t>
+    <t>2023-11-28T12:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1660,6 +1660,39 @@
   </si>
   <si>
     <t>methodCode</t>
+  </si>
+  <si>
+    <t>Observation.method.id</t>
+  </si>
+  <si>
+    <t>Observation.method.extension</t>
+  </si>
+  <si>
+    <t>Observation.method.coding</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.id</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.extension</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.system</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.version</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.code</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.display</t>
+  </si>
+  <si>
+    <t>Observation.method.coding.userSelected</t>
+  </si>
+  <si>
+    <t>Observation.method.text</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -2368,7 +2401,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP95"/>
+  <dimension ref="A1:AP106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
@@ -11013,7 +11046,7 @@
         <v>91</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>80</v>
@@ -11059,9 +11092,11 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y72" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>525</v>
+      </c>
       <c r="Z72" t="s" s="2">
         <v>525</v>
       </c>
@@ -11142,17 +11177,15 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>529</v>
+        <v>107</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>530</v>
+        <v>108</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>532</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -11201,7 +11234,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>528</v>
+        <v>110</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11210,47 +11243,47 @@
         <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>228</v>
+        <v>80</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>533</v>
+        <v>80</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>534</v>
+        <v>80</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>535</v>
+        <v>111</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>536</v>
+        <v>80</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
@@ -11262,16 +11295,16 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>538</v>
+        <v>114</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>539</v>
+        <v>115</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>540</v>
+        <v>116</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>541</v>
+        <v>117</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11309,57 +11342,57 @@
         <v>80</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>537</v>
+        <v>121</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>228</v>
+        <v>122</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>542</v>
+        <v>80</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>543</v>
+        <v>80</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>544</v>
+        <v>105</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>545</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>546</v>
+        <v>530</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11379,22 +11412,22 @@
         <v>80</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>547</v>
+        <v>147</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>548</v>
+        <v>274</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>549</v>
+        <v>275</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>550</v>
+        <v>276</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>551</v>
+        <v>277</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11443,7 +11476,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>546</v>
+        <v>278</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11455,7 +11488,7 @@
         <v>103</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>552</v>
+        <v>104</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
@@ -11464,10 +11497,10 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>553</v>
+        <v>279</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>554</v>
+        <v>280</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11478,10 +11511,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>555</v>
+        <v>531</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>555</v>
+        <v>531</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11596,10 +11629,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>556</v>
+        <v>532</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>556</v>
+        <v>532</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11716,45 +11749,45 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>557</v>
+        <v>533</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>557</v>
+        <v>533</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>558</v>
+        <v>80</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J78" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>559</v>
+        <v>287</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>560</v>
+        <v>288</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>117</v>
+        <v>289</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>210</v>
+        <v>290</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11803,19 +11836,19 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>561</v>
+        <v>292</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>122</v>
+        <v>104</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>80</v>
@@ -11824,10 +11857,10 @@
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>80</v>
+        <v>293</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>105</v>
+        <v>294</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11838,10 +11871,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>562</v>
+        <v>534</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>562</v>
+        <v>534</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11861,19 +11894,19 @@
         <v>80</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>563</v>
+        <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>564</v>
+        <v>297</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>565</v>
+        <v>298</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>566</v>
+        <v>299</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11923,7 +11956,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>562</v>
+        <v>300</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11932,10 +11965,10 @@
         <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>567</v>
+        <v>103</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>568</v>
+        <v>104</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11944,10 +11977,10 @@
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>569</v>
+        <v>301</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>570</v>
+        <v>302</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -11958,10 +11991,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>571</v>
+        <v>535</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>571</v>
+        <v>535</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11969,7 +12002,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>91</v>
@@ -11981,21 +12014,23 @@
         <v>80</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>563</v>
+        <v>171</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>572</v>
+        <v>305</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>573</v>
+        <v>306</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O80" s="2"/>
+        <v>307</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
       </c>
@@ -12043,7 +12078,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>571</v>
+        <v>310</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12052,10 +12087,10 @@
         <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>567</v>
+        <v>103</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>568</v>
+        <v>104</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>80</v>
@@ -12064,10 +12099,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>569</v>
+        <v>311</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>574</v>
+        <v>312</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12078,10 +12113,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>575</v>
+        <v>536</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>575</v>
+        <v>536</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12101,22 +12136,22 @@
         <v>80</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>576</v>
+        <v>315</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>577</v>
+        <v>316</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>578</v>
+        <v>307</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>579</v>
+        <v>317</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -12141,13 +12176,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>581</v>
+        <v>80</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -12165,7 +12200,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>575</v>
+        <v>318</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12183,13 +12218,13 @@
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>582</v>
+        <v>80</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>583</v>
+        <v>319</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12200,10 +12235,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>584</v>
+        <v>537</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>584</v>
+        <v>537</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12214,7 +12249,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -12223,22 +12258,22 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>255</v>
+        <v>323</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>585</v>
+        <v>324</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>586</v>
+        <v>325</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>587</v>
+        <v>326</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>588</v>
+        <v>327</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -12263,13 +12298,13 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>161</v>
+        <v>80</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>589</v>
+        <v>80</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>590</v>
+        <v>80</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>80</v>
@@ -12287,13 +12322,13 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>584</v>
+        <v>328</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>103</v>
@@ -12305,13 +12340,13 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>582</v>
+        <v>80</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>583</v>
+        <v>329</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>500</v>
+        <v>330</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12322,10 +12357,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>591</v>
+        <v>538</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>591</v>
+        <v>538</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12345,22 +12380,22 @@
         <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>592</v>
+        <v>107</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>593</v>
+        <v>333</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>594</v>
+        <v>334</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>595</v>
+        <v>335</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>596</v>
+        <v>336</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -12409,7 +12444,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>591</v>
+        <v>337</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12421,7 +12456,7 @@
         <v>103</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>597</v>
+        <v>104</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
@@ -12430,10 +12465,10 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>598</v>
+        <v>338</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>599</v>
+        <v>339</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -12444,10 +12479,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>600</v>
+        <v>539</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>600</v>
+        <v>539</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12470,16 +12505,16 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>107</v>
+        <v>540</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>601</v>
+        <v>541</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>602</v>
+        <v>542</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>307</v>
+        <v>543</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12529,7 +12564,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>600</v>
+        <v>539</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12541,33 +12576,33 @@
         <v>103</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>104</v>
+        <v>228</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>80</v>
+        <v>544</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>569</v>
+        <v>545</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>603</v>
+        <v>546</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>80</v>
+        <v>547</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>604</v>
+        <v>548</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>604</v>
+        <v>548</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12578,7 +12613,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12587,19 +12622,19 @@
         <v>80</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>605</v>
+        <v>549</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>606</v>
+        <v>550</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>607</v>
+        <v>551</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>608</v>
+        <v>552</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12649,13 +12684,13 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>604</v>
+        <v>548</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>103</v>
@@ -12667,27 +12702,27 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>80</v>
+        <v>553</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>609</v>
+        <v>554</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>610</v>
+        <v>555</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>80</v>
+        <v>556</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>611</v>
+        <v>557</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>611</v>
+        <v>557</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12707,21 +12742,23 @@
         <v>80</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>612</v>
+        <v>558</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>613</v>
+        <v>559</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>614</v>
+        <v>560</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="O86" s="2"/>
+        <v>561</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>562</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>80</v>
       </c>
@@ -12769,7 +12806,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>611</v>
+        <v>557</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12781,7 +12818,7 @@
         <v>103</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>228</v>
+        <v>563</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>80</v>
@@ -12790,10 +12827,10 @@
         <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>609</v>
+        <v>564</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>616</v>
+        <v>565</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -12804,10 +12841,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>617</v>
+        <v>566</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>617</v>
+        <v>566</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12818,32 +12855,28 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>547</v>
+        <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>618</v>
+        <v>108</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>620</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>80</v>
       </c>
@@ -12891,19 +12924,19 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>617</v>
+        <v>110</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>621</v>
+        <v>80</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>80</v>
@@ -12912,10 +12945,10 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>622</v>
+        <v>80</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>623</v>
+        <v>111</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -12926,21 +12959,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>624</v>
+        <v>567</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>624</v>
+        <v>567</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>80</v>
@@ -12952,15 +12985,17 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N88" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -12997,31 +13032,31 @@
         <v>80</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>80</v>
+        <v>122</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
@@ -13033,7 +13068,7 @@
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13044,14 +13079,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>625</v>
+        <v>568</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>625</v>
+        <v>568</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>113</v>
+        <v>569</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13064,24 +13099,26 @@
         <v>80</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>115</v>
+        <v>570</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>116</v>
+        <v>571</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>80</v>
       </c>
@@ -13117,19 +13154,19 @@
         <v>80</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>121</v>
+        <v>572</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13164,46 +13201,44 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>626</v>
+        <v>573</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>626</v>
+        <v>573</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>558</v>
+        <v>80</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>114</v>
+        <v>574</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>559</v>
+        <v>575</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>560</v>
+        <v>576</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>80</v>
       </c>
@@ -13251,19 +13286,19 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>103</v>
+        <v>578</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>122</v>
+        <v>579</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
@@ -13272,10 +13307,10 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>105</v>
+        <v>581</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13286,10 +13321,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>627</v>
+        <v>582</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>627</v>
+        <v>582</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13297,35 +13332,33 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>255</v>
+        <v>574</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>628</v>
+        <v>583</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>629</v>
+        <v>584</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>631</v>
-      </c>
+        <v>577</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13349,13 +13382,13 @@
         <v>80</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>346</v>
+        <v>80</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>347</v>
+        <v>80</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>80</v>
@@ -13373,34 +13406,34 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>627</v>
+        <v>582</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>103</v>
+        <v>578</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>104</v>
+        <v>579</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>632</v>
+        <v>80</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>350</v>
+        <v>580</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>351</v>
+        <v>585</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>352</v>
+        <v>80</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>80</v>
@@ -13408,10 +13441,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>633</v>
+        <v>586</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>633</v>
+        <v>586</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13425,28 +13458,28 @@
         <v>91</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>634</v>
+        <v>255</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>635</v>
+        <v>587</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>636</v>
+        <v>588</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>637</v>
+        <v>589</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>419</v>
+        <v>590</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13471,13 +13504,13 @@
         <v>80</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>246</v>
+        <v>175</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>638</v>
+        <v>591</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>639</v>
+        <v>592</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
@@ -13495,7 +13528,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>633</v>
+        <v>586</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13504,7 +13537,7 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>640</v>
+        <v>103</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>104</v>
@@ -13513,27 +13546,27 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>641</v>
+        <v>593</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>423</v>
+        <v>594</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>424</v>
+        <v>500</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>425</v>
+        <v>80</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>642</v>
+        <v>595</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>642</v>
+        <v>595</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13544,10 +13577,10 @@
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>80</v>
@@ -13559,16 +13592,16 @@
         <v>255</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>643</v>
+        <v>596</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>644</v>
+        <v>597</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>645</v>
+        <v>598</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>474</v>
+        <v>599</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13593,13 +13626,13 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>475</v>
+        <v>600</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>476</v>
+        <v>601</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13617,16 +13650,16 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>642</v>
+        <v>595</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>646</v>
+        <v>103</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>104</v>
@@ -13635,13 +13668,13 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>80</v>
+        <v>593</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>105</v>
+        <v>594</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>478</v>
+        <v>500</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13652,21 +13685,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>647</v>
+        <v>602</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>647</v>
+        <v>602</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>491</v>
+        <v>80</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>80</v>
@@ -13678,19 +13711,19 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>255</v>
+        <v>603</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>492</v>
+        <v>604</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>493</v>
+        <v>605</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>494</v>
+        <v>606</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>495</v>
+        <v>607</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13715,13 +13748,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>151</v>
+        <v>80</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>496</v>
+        <v>80</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>497</v>
+        <v>80</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13739,45 +13772,45 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>647</v>
+        <v>602</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>104</v>
+        <v>608</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>498</v>
+        <v>80</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>499</v>
+        <v>609</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>500</v>
+        <v>610</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>501</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>648</v>
+        <v>611</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>648</v>
+        <v>611</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13788,7 +13821,7 @@
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>80</v>
@@ -13800,20 +13833,18 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>649</v>
+        <v>612</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>650</v>
+        <v>613</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>551</v>
-      </c>
+        <v>307</v>
+      </c>
+      <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>80</v>
       </c>
@@ -13861,41 +13892,1373 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="O97" s="2"/>
+      <c r="P97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O100" s="2"/>
+      <c r="P100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O101" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="P101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>639</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="O102" t="s" s="2">
+        <v>642</v>
+      </c>
+      <c r="P102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="N103" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="AG95" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH95" t="s" s="2">
+      <c r="O103" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>649</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>644</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>655</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>91</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>657</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G105" t="s" s="2">
         <v>79</v>
       </c>
-      <c r="AI95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP95" t="s" s="2">
+      <c r="H105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="P105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AP106" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP95">
+  <autoFilter ref="A1:AP106">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -13905,7 +15268,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI94">
+  <conditionalFormatting sqref="A2:AI105">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4108" uniqueCount="662">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3685" uniqueCount="651">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:22:20+00:00</t>
+    <t>2023-11-28T12:44:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1660,39 +1660,6 @@
   </si>
   <si>
     <t>methodCode</t>
-  </si>
-  <si>
-    <t>Observation.method.id</t>
-  </si>
-  <si>
-    <t>Observation.method.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.id</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.extension</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.system</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.version</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.code</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.display</t>
-  </si>
-  <si>
-    <t>Observation.method.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Observation.method.text</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -2401,7 +2368,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP106"/>
+  <dimension ref="A1:AP95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.3046875" customWidth="true" bestFit="true"/>
@@ -11046,7 +11013,7 @@
         <v>91</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>80</v>
@@ -11092,11 +11059,9 @@
         <v>80</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>525</v>
-      </c>
+        <v>151</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
         <v>525</v>
       </c>
@@ -11177,15 +11142,17 @@
         <v>80</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>107</v>
+        <v>529</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>108</v>
+        <v>530</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>531</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>532</v>
+      </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -11234,7 +11201,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>110</v>
+        <v>528</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11243,47 +11210,47 @@
         <v>91</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>80</v>
+        <v>228</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>80</v>
+        <v>533</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>80</v>
+        <v>534</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>111</v>
+        <v>535</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>80</v>
+        <v>536</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>529</v>
+        <v>537</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>80</v>
@@ -11295,16 +11262,16 @@
         <v>80</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>114</v>
+        <v>538</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>115</v>
+        <v>539</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>116</v>
+        <v>540</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>117</v>
+        <v>541</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -11342,57 +11309,57 @@
         <v>80</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>121</v>
+        <v>537</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>122</v>
+        <v>228</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>80</v>
+        <v>542</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>80</v>
+        <v>543</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>105</v>
+        <v>544</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>80</v>
+        <v>545</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11412,22 +11379,22 @@
         <v>80</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>147</v>
+        <v>547</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>274</v>
+        <v>548</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>275</v>
+        <v>549</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>276</v>
+        <v>550</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>277</v>
+        <v>551</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>80</v>
@@ -11476,7 +11443,7 @@
         <v>80</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>278</v>
+        <v>546</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11488,7 +11455,7 @@
         <v>103</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>104</v>
+        <v>552</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>80</v>
@@ -11497,10 +11464,10 @@
         <v>80</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>279</v>
+        <v>553</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>280</v>
+        <v>554</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>80</v>
@@ -11511,10 +11478,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>531</v>
+        <v>555</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11629,10 +11596,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>532</v>
+        <v>556</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11749,45 +11716,45 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>533</v>
+        <v>557</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>80</v>
+        <v>558</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J78" t="s" s="2">
         <v>92</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>287</v>
+        <v>559</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>288</v>
+        <v>560</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>289</v>
+        <v>117</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -11836,19 +11803,19 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>292</v>
+        <v>561</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>80</v>
@@ -11857,10 +11824,10 @@
         <v>80</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>293</v>
+        <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>294</v>
+        <v>105</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -11871,10 +11838,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>534</v>
+        <v>562</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>534</v>
+        <v>562</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11894,19 +11861,19 @@
         <v>80</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>107</v>
+        <v>563</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>297</v>
+        <v>564</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>298</v>
+        <v>565</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>299</v>
+        <v>566</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -11956,7 +11923,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>300</v>
+        <v>562</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11965,10 +11932,10 @@
         <v>91</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>103</v>
+        <v>567</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>104</v>
+        <v>568</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>80</v>
@@ -11977,10 +11944,10 @@
         <v>80</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>301</v>
+        <v>569</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>302</v>
+        <v>570</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -11991,10 +11958,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>535</v>
+        <v>571</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>535</v>
+        <v>571</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12002,7 +11969,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>91</v>
@@ -12014,23 +11981,21 @@
         <v>80</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>171</v>
+        <v>563</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>305</v>
+        <v>572</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>306</v>
+        <v>573</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>566</v>
+      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>80</v>
       </c>
@@ -12078,7 +12043,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>310</v>
+        <v>571</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -12087,10 +12052,10 @@
         <v>91</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>103</v>
+        <v>567</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>104</v>
+        <v>568</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>80</v>
@@ -12099,10 +12064,10 @@
         <v>80</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>311</v>
+        <v>569</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>312</v>
+        <v>574</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -12113,10 +12078,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>536</v>
+        <v>575</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>536</v>
+        <v>575</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12136,22 +12101,22 @@
         <v>80</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>107</v>
+        <v>255</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>315</v>
+        <v>576</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>316</v>
+        <v>577</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>307</v>
+        <v>578</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>317</v>
+        <v>579</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -12176,13 +12141,13 @@
         <v>80</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>80</v>
+        <v>175</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>80</v>
+        <v>580</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>80</v>
+        <v>581</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>80</v>
@@ -12200,7 +12165,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>318</v>
+        <v>575</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12218,13 +12183,13 @@
         <v>80</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>80</v>
+        <v>582</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>319</v>
+        <v>583</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>320</v>
+        <v>500</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -12235,10 +12200,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>537</v>
+        <v>584</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12249,7 +12214,7 @@
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>80</v>
@@ -12258,22 +12223,22 @@
         <v>80</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>323</v>
+        <v>255</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>324</v>
+        <v>585</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>325</v>
+        <v>586</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>326</v>
+        <v>587</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>327</v>
+        <v>588</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>80</v>
@@ -12298,13 +12263,13 @@
         <v>80</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>80</v>
+        <v>161</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>80</v>
+        <v>589</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>80</v>
+        <v>590</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>80</v>
@@ -12322,13 +12287,13 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>328</v>
+        <v>584</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>103</v>
@@ -12340,13 +12305,13 @@
         <v>80</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>80</v>
+        <v>582</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>329</v>
+        <v>583</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>330</v>
+        <v>500</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>80</v>
@@ -12357,10 +12322,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>538</v>
+        <v>591</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>538</v>
+        <v>591</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12380,22 +12345,22 @@
         <v>80</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>107</v>
+        <v>592</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>333</v>
+        <v>593</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>334</v>
+        <v>594</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>335</v>
+        <v>595</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>336</v>
+        <v>596</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>80</v>
@@ -12444,7 +12409,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>337</v>
+        <v>591</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12456,7 +12421,7 @@
         <v>103</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>104</v>
+        <v>597</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>80</v>
@@ -12465,10 +12430,10 @@
         <v>80</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>338</v>
+        <v>598</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>339</v>
+        <v>599</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
@@ -12479,10 +12444,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>539</v>
+        <v>600</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>539</v>
+        <v>600</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12505,16 +12470,16 @@
         <v>80</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>540</v>
+        <v>107</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>541</v>
+        <v>601</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>542</v>
+        <v>602</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>543</v>
+        <v>307</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12564,7 +12529,7 @@
         <v>80</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>539</v>
+        <v>600</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12576,33 +12541,33 @@
         <v>103</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>228</v>
+        <v>104</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>544</v>
+        <v>80</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>545</v>
+        <v>569</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>546</v>
+        <v>603</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>547</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12613,7 +12578,7 @@
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>80</v>
@@ -12622,19 +12587,19 @@
         <v>80</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>549</v>
+        <v>605</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>550</v>
+        <v>606</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>551</v>
+        <v>607</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>552</v>
+        <v>608</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12684,13 +12649,13 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>103</v>
@@ -12702,27 +12667,27 @@
         <v>80</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>553</v>
+        <v>80</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>554</v>
+        <v>609</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>555</v>
+        <v>610</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>556</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>557</v>
+        <v>611</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>557</v>
+        <v>611</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12742,23 +12707,21 @@
         <v>80</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>558</v>
+        <v>612</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>559</v>
+        <v>613</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>560</v>
+        <v>614</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>562</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>80</v>
       </c>
@@ -12806,7 +12769,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>557</v>
+        <v>611</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12818,7 +12781,7 @@
         <v>103</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>563</v>
+        <v>228</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>80</v>
@@ -12827,10 +12790,10 @@
         <v>80</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>564</v>
+        <v>609</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>565</v>
+        <v>616</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>80</v>
@@ -12841,10 +12804,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>566</v>
+        <v>617</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>566</v>
+        <v>617</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12855,28 +12818,32 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>107</v>
+        <v>547</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>108</v>
+        <v>618</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>618</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>620</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>80</v>
       </c>
@@ -12924,19 +12891,19 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>110</v>
+        <v>617</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>80</v>
+        <v>621</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>80</v>
@@ -12945,10 +12912,10 @@
         <v>80</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>80</v>
+        <v>622</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>111</v>
+        <v>623</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -12959,21 +12926,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>567</v>
+        <v>624</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>567</v>
+        <v>624</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>113</v>
+        <v>80</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>80</v>
@@ -12985,17 +12952,15 @@
         <v>80</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>80</v>
@@ -13032,31 +12997,31 @@
         <v>80</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>119</v>
+        <v>80</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>122</v>
+        <v>80</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>80</v>
@@ -13068,7 +13033,7 @@
         <v>80</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -13079,14 +13044,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>568</v>
+        <v>625</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>568</v>
+        <v>625</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>569</v>
+        <v>113</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13099,26 +13064,24 @@
         <v>80</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="K89" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>570</v>
+        <v>115</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>571</v>
+        <v>116</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O89" t="s" s="2">
-        <v>210</v>
-      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>80</v>
       </c>
@@ -13154,19 +13117,19 @@
         <v>80</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>572</v>
+        <v>121</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13201,44 +13164,46 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>573</v>
+        <v>626</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>573</v>
+        <v>626</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>80</v>
+        <v>558</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="I90" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>574</v>
+        <v>114</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>575</v>
+        <v>559</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>576</v>
+        <v>560</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>117</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>80</v>
       </c>
@@ -13286,19 +13251,19 @@
         <v>80</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>578</v>
+        <v>103</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>579</v>
+        <v>122</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>80</v>
@@ -13307,10 +13272,10 @@
         <v>80</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>581</v>
+        <v>105</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>80</v>
@@ -13321,10 +13286,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>582</v>
+        <v>627</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>582</v>
+        <v>627</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13332,33 +13297,35 @@
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="G91" t="s" s="2">
         <v>91</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>574</v>
+        <v>255</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>583</v>
+        <v>628</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>584</v>
+        <v>629</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>630</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
       </c>
@@ -13382,13 +13349,13 @@
         <v>80</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>80</v>
+        <v>346</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>80</v>
+        <v>347</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>80</v>
@@ -13406,34 +13373,34 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>582</v>
+        <v>627</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>91</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>578</v>
+        <v>103</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>579</v>
+        <v>104</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>80</v>
+        <v>632</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>580</v>
+        <v>350</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>585</v>
+        <v>351</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>80</v>
+        <v>352</v>
       </c>
       <c r="AP91" t="s" s="2">
         <v>80</v>
@@ -13441,10 +13408,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13458,28 +13425,28 @@
         <v>91</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>255</v>
+        <v>634</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>587</v>
+        <v>635</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>588</v>
+        <v>636</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>589</v>
+        <v>637</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>590</v>
+        <v>419</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>80</v>
@@ -13504,13 +13471,13 @@
         <v>80</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>175</v>
+        <v>246</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>591</v>
+        <v>638</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>592</v>
+        <v>639</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
@@ -13528,7 +13495,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>586</v>
+        <v>633</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13537,7 +13504,7 @@
         <v>91</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>103</v>
+        <v>640</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>104</v>
@@ -13546,27 +13513,27 @@
         <v>80</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>593</v>
+        <v>641</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>594</v>
+        <v>423</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>500</v>
+        <v>424</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>80</v>
+        <v>425</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>595</v>
+        <v>642</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>595</v>
+        <v>642</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13577,10 +13544,10 @@
         <v>78</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>80</v>
@@ -13592,16 +13559,16 @@
         <v>255</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>596</v>
+        <v>643</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>597</v>
+        <v>644</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>598</v>
+        <v>645</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>599</v>
+        <v>474</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>80</v>
@@ -13626,13 +13593,13 @@
         <v>80</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>600</v>
+        <v>475</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>601</v>
+        <v>476</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>80</v>
@@ -13650,16 +13617,16 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>595</v>
+        <v>642</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>103</v>
+        <v>646</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>104</v>
@@ -13668,13 +13635,13 @@
         <v>80</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>593</v>
+        <v>80</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>594</v>
+        <v>105</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>500</v>
+        <v>478</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -13685,21 +13652,21 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>602</v>
+        <v>647</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>602</v>
+        <v>647</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>80</v>
+        <v>491</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H94" t="s" s="2">
         <v>80</v>
@@ -13711,19 +13678,19 @@
         <v>80</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>603</v>
+        <v>255</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>604</v>
+        <v>492</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>605</v>
+        <v>493</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>606</v>
+        <v>494</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>607</v>
+        <v>495</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -13748,13 +13715,13 @@
         <v>80</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>80</v>
+        <v>151</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>80</v>
+        <v>496</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>80</v>
+        <v>497</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>80</v>
@@ -13772,45 +13739,45 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>602</v>
+        <v>647</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>103</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>608</v>
+        <v>104</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>80</v>
+        <v>498</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>609</v>
+        <v>499</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>610</v>
+        <v>500</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>80</v>
+        <v>501</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13821,7 +13788,7 @@
         <v>78</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>80</v>
@@ -13833,18 +13800,20 @@
         <v>80</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>612</v>
+        <v>649</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>613</v>
+        <v>650</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="O95" s="2"/>
+        <v>550</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>551</v>
+      </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
       </c>
@@ -13892,19 +13861,19 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>611</v>
+        <v>648</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="AI95" t="s" s="2">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>104</v>
+        <v>80</v>
       </c>
       <c r="AK95" t="s" s="2">
         <v>80</v>
@@ -13913,1352 +13882,20 @@
         <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>580</v>
+        <v>553</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>614</v>
+        <v>554</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="O96" s="2"/>
-      <c r="P96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="O97" s="2"/>
-      <c r="P97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>633</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>634</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>635</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" s="2"/>
-      <c r="P99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>636</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O100" s="2"/>
-      <c r="P100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="P101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>639</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>640</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>641</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="P102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>643</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>645</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>644</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="N104" t="s" s="2">
-        <v>656</v>
-      </c>
-      <c r="O104" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>476</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>657</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="O105" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>496</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>497</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>658</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>659</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AP106" t="s" s="2">
         <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP106">
+  <autoFilter ref="A1:AP95">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15268,7 +13905,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI105">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T12:44:29+00:00</t>
+    <t>2023-11-28T13:07:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:07:26+00:00</t>
+    <t>2023-11-28T13:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1697,12 +1697,11 @@
 </t>
   </si>
   <si>
-    <t>Dispositif utilisé pour l'observation</t>
-  </si>
-  <si>
     <t>Dispositif utilisé pour l'observation
-Si la mesure a été faite par un objet connecté (Profil PhdDevice)
-=&gt;cette référence est obligatoire</t>
+Si la mesure a été faite par un objet connecté (Profil PhdDevice), cette référence est obligatoire</t>
+  </si>
+  <si>
+    <t>The device used to generate the observation data.</t>
   </si>
   <si>
     <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
@@ -11253,7 +11252,7 @@
         <v>91</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>80</v>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:18:47+00:00</t>
+    <t>2023-11-28T13:27:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:27:45+00:00</t>
+    <t>2023-11-28T13:42:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-28T13:42:11+00:00</t>
+    <t>2023-12-08T09:30:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-13T10:33:05+00:00</t>
+    <t>2023-12-29T10:04:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T10:04:05+00:00</t>
+    <t>2024-02-01T10:35:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T10:35:02+00:00</t>
+    <t>2024-02-01T13:55:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:55:30+00:00</t>
+    <t>2024-02-01T13:56:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T13:56:11+00:00</t>
+    <t>2024-02-01T14:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T14:29:51+00:00</t>
+    <t>2024-02-01T16:04:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-01T16:04:25+00:00</t>
+    <t>2024-02-05T14:48:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1131,8 +1131,8 @@
     <t>Observation.code.coding</t>
   </si>
   <si>
-    <t>value:code}
-value:system}</t>
+    <t>pattern:code}
+pattern:system}</t>
   </si>
   <si>
     <t>Observation.code.coding:stepsBDCode</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-05T14:48:49+00:00</t>
+    <t>2024-02-12T14:46:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:46:58+00:00</t>
+    <t>2024-02-12T14:53:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
+++ b/ig/main/StructureDefinition-mesures-observation-steps-by-day.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:53:29+00:00</t>
+    <t>2024-04-08T08:01:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>ANS (https://esante.gouv.fr)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
